--- a/第九道题：选一道题/A题/附件A 订购方案数据结果.xlsx
+++ b/第九道题：选一道题/A题/附件A 订购方案数据结果.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,14 +10,14 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF6EF31-7A42-4FF6-80DF-BA73BB860846}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="555" windowWidth="21600" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="885" yWindow="555" windowWidth="21600" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="问题2的订购方案结果" sheetId="1" r:id="rId1"/>
     <sheet name="问题3的订购方案结果" sheetId="2" r:id="rId2"/>
     <sheet name="问题4的订购方案结果" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1296" uniqueCount="436">
   <si>
     <t>1.请不要修改表格中已有的任何信息；</t>
   </si>
@@ -1352,8 +1352,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1434,24 +1434,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79998168889431"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.79998168889431"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1461,94 +1461,96 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1567,7 +1569,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1684,7 +1686,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1708,9 +1710,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1734,7 +1736,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1769,7 +1771,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1787,7 +1789,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1812,7 +1814,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1823,37 +1825,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:Y409"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="12.86328125" customWidth="true"/>
+    <col min="3" max="3" width="14.86328125" customWidth="true"/>
+    <col min="4" max="4" width="12.86328125" customWidth="true"/>
+    <col min="5" max="5" width="12.86328125" customWidth="true"/>
+    <col min="6" max="6" width="12.86328125" customWidth="true"/>
+    <col min="7" max="7" width="12.86328125" customWidth="true"/>
+    <col min="8" max="8" width="12.86328125" customWidth="true"/>
+    <col min="9" max="9" width="12.86328125" customWidth="true"/>
+    <col min="10" max="10" width="12.86328125" customWidth="true"/>
+    <col min="11" max="11" width="12.86328125" customWidth="true"/>
+    <col min="12" max="12" width="12.86328125" customWidth="true"/>
+    <col min="13" max="13" width="12.86328125" customWidth="true"/>
+    <col min="14" max="14" width="12.86328125" customWidth="true"/>
+    <col min="15" max="15" width="12.86328125" customWidth="true"/>
+    <col min="16" max="16" width="12.86328125" customWidth="true"/>
+    <col min="17" max="17" width="12.86328125" customWidth="true"/>
+    <col min="18" max="18" width="12.86328125" customWidth="true"/>
+    <col min="19" max="19" width="12.86328125" customWidth="true"/>
+    <col min="20" max="20" width="12.86328125" customWidth="true"/>
+    <col min="21" max="21" width="12.86328125" customWidth="true"/>
+    <col min="22" max="22" width="12.86328125" customWidth="true"/>
+    <col min="23" max="23" width="12.86328125" customWidth="true"/>
+    <col min="24" max="24" width="12.86328125" customWidth="true"/>
+    <col min="25" max="25" width="12.86328125" customWidth="true"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" s="1" customFormat="true" x14ac:dyDescent="0.15">
       <c r="A1" s="12" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" s="1" customFormat="true" x14ac:dyDescent="0.15">
       <c r="A2" s="12" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" s="1" customFormat="true" x14ac:dyDescent="0.15">
       <c r="A3" s="12" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" s="1" customFormat="true" x14ac:dyDescent="0.15">
       <c r="A4" s="13" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="5" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" s="1" customFormat="true" x14ac:dyDescent="0.15">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" s="1" customFormat="true" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>427</v>
       </c>
@@ -1930,7 +1958,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
@@ -1959,7 +1987,7 @@
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -1988,36 +2016,54 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="3">
+        <v>166.13325686546855</v>
+      </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="D9" s="3">
+        <v>201.99999999999989</v>
+      </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3">
+        <v>179.91357709727717</v>
+      </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="3">
+        <v>194.1174775838422</v>
+      </c>
+      <c r="I9" s="3">
+        <v>176.26795437448635</v>
+      </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>145.92985843400376</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
+      <c r="Q9" s="3">
+        <v>172.29225630248379</v>
+      </c>
       <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
+      <c r="S9" s="3">
+        <v>170.67200854982727</v>
+      </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+      <c r="V9" s="3">
+        <v>187.62140668729523</v>
+      </c>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
@@ -2046,36 +2092,78 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="3">
+        <v>77.034239377984406</v>
+      </c>
+      <c r="C11" s="3">
+        <v>80</v>
+      </c>
+      <c r="D11" s="3">
+        <v>77.428727681087409</v>
+      </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="F11" s="3">
+        <v>80.000000000000014</v>
+      </c>
+      <c r="G11" s="3">
+        <v>79.318210467430021</v>
+      </c>
+      <c r="H11" s="3">
+        <v>80</v>
+      </c>
+      <c r="I11" s="3">
+        <v>78.345766688477923</v>
+      </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
+      <c r="K11" s="3">
+        <v>79.240269044593035</v>
+      </c>
+      <c r="L11" s="3">
+        <v>74.446760661781056</v>
+      </c>
+      <c r="M11" s="3">
+        <v>76.346973640723022</v>
+      </c>
+      <c r="N11" s="3">
+        <v>76.502311502295015</v>
+      </c>
+      <c r="O11" s="3">
+        <v>79.909845706296721</v>
+      </c>
+      <c r="P11" s="3">
+        <v>78.056113172257682</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>79.898269460796541</v>
+      </c>
+      <c r="R11" s="3">
+        <v>78.167359797468023</v>
+      </c>
+      <c r="S11" s="3">
+        <v>77.043598444202402</v>
+      </c>
+      <c r="T11" s="3">
+        <v>77.890675257618966</v>
+      </c>
       <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="V11" s="3">
+        <v>80</v>
+      </c>
+      <c r="W11" s="3">
+        <v>80</v>
+      </c>
+      <c r="X11" s="3">
+        <v>80.000000000000014</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>78.8724940795355</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
@@ -2104,36 +2192,82 @@
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="B13" s="3">
+        <v>52.587023731522862</v>
+      </c>
+      <c r="C13" s="3">
+        <v>56.533300195522145</v>
+      </c>
+      <c r="D13" s="3">
+        <v>55.943749585569144</v>
+      </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="F13" s="3">
+        <v>50.672278535877489</v>
+      </c>
+      <c r="G13" s="3">
+        <v>37.912586490647023</v>
+      </c>
+      <c r="H13" s="3">
+        <v>44.691053124029054</v>
+      </c>
+      <c r="I13" s="3">
+        <v>48.477799663465007</v>
+      </c>
+      <c r="J13" s="3">
+        <v>41.519882456978493</v>
+      </c>
+      <c r="K13" s="3">
+        <v>41.789453371595137</v>
+      </c>
+      <c r="L13" s="3">
+        <v>52.683871365889679</v>
+      </c>
+      <c r="M13" s="3">
+        <v>39.122400009473161</v>
+      </c>
+      <c r="N13" s="3">
+        <v>39.972770158259543</v>
+      </c>
+      <c r="O13" s="3">
+        <v>44.768764739163643</v>
+      </c>
+      <c r="P13" s="3">
+        <v>39.122400009473161</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>44.306507085441389</v>
+      </c>
+      <c r="R13" s="3">
+        <v>44.382885965714529</v>
+      </c>
+      <c r="S13" s="3">
+        <v>45.967738683891263</v>
+      </c>
+      <c r="T13" s="3">
+        <v>47.581868532290571</v>
+      </c>
+      <c r="U13" s="3">
+        <v>46.803381348123786</v>
+      </c>
+      <c r="V13" s="3">
+        <v>55.002424035572979</v>
+      </c>
+      <c r="W13" s="3">
+        <v>44.078939635977363</v>
+      </c>
+      <c r="X13" s="3">
+        <v>45.80417817019918</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>53.795697380351349</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -2162,7 +2296,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
@@ -2191,7 +2325,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -2220,7 +2354,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>35</v>
       </c>
@@ -2249,7 +2383,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
@@ -2278,7 +2412,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>37</v>
       </c>
@@ -2307,7 +2441,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>38</v>
       </c>
@@ -2336,7 +2470,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>39</v>
       </c>
@@ -2365,7 +2499,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>40</v>
       </c>
@@ -2394,7 +2528,7 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>41</v>
       </c>
@@ -2423,7 +2557,7 @@
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>42</v>
       </c>
@@ -2452,7 +2586,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>43</v>
       </c>
@@ -2481,7 +2615,7 @@
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
         <v>44</v>
       </c>
@@ -2510,7 +2644,7 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>45</v>
       </c>
@@ -2539,7 +2673,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>46</v>
       </c>
@@ -2568,7 +2702,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>47</v>
       </c>
@@ -2597,7 +2731,7 @@
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>48</v>
       </c>
@@ -2626,7 +2760,7 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>49</v>
       </c>
@@ -2655,7 +2789,7 @@
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>50</v>
       </c>
@@ -2684,7 +2818,7 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>51</v>
       </c>
@@ -2713,7 +2847,7 @@
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>52</v>
       </c>
@@ -2742,7 +2876,7 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
         <v>53</v>
       </c>
@@ -2771,7 +2905,7 @@
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
         <v>54</v>
       </c>
@@ -2800,7 +2934,7 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
         <v>55</v>
       </c>
@@ -2829,7 +2963,7 @@
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="38" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
         <v>56</v>
       </c>
@@ -2858,7 +2992,7 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="39" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
         <v>57</v>
       </c>
@@ -2887,7 +3021,7 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="40" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
         <v>58</v>
       </c>
@@ -2916,7 +3050,7 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="41" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
         <v>59</v>
       </c>
@@ -2945,7 +3079,7 @@
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="42" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
         <v>60</v>
       </c>
@@ -2974,36 +3108,58 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="43" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="B43" s="3">
+        <v>1051.5642184963429</v>
+      </c>
+      <c r="C43" s="3">
+        <v>640.52620358367926</v>
+      </c>
+      <c r="D43" s="3">
+        <v>992.26621430065291</v>
+      </c>
       <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="F43" s="3">
+        <v>992.26621430065291</v>
+      </c>
       <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
+      <c r="H43" s="3">
+        <v>798.54150243959339</v>
+      </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
+      <c r="K43" s="3">
+        <v>865.42700031159666</v>
+      </c>
       <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
+      <c r="M43" s="3">
+        <v>1348.2390367440885</v>
+      </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
-      <c r="Q43" s="3"/>
+      <c r="Q43" s="3">
+        <v>635.77265090912226</v>
+      </c>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
+      <c r="V43" s="3">
+        <v>998.3506503514501</v>
+      </c>
+      <c r="W43" s="3">
+        <v>695.63154332666807</v>
+      </c>
       <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Y43" s="3">
+        <v>593.01593284043975</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="44" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
         <v>62</v>
       </c>
@@ -3032,7 +3188,7 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="45" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
         <v>63</v>
       </c>
@@ -3061,7 +3217,7 @@
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="46" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
         <v>64</v>
       </c>
@@ -3090,7 +3246,7 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="47" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
         <v>65</v>
       </c>
@@ -3119,7 +3275,7 @@
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="48" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
         <v>66</v>
       </c>
@@ -3148,7 +3304,7 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="49" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
         <v>67</v>
       </c>
@@ -3177,7 +3333,7 @@
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="50" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
         <v>68</v>
       </c>
@@ -3206,7 +3362,7 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="51" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
         <v>69</v>
       </c>
@@ -3235,7 +3391,7 @@
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="52" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
         <v>70</v>
       </c>
@@ -3264,7 +3420,7 @@
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="53" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
         <v>71</v>
       </c>
@@ -3293,7 +3449,7 @@
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="54" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
         <v>72</v>
       </c>
@@ -3322,7 +3478,7 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="55" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
         <v>73</v>
       </c>
@@ -3351,7 +3507,7 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="56" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
         <v>74</v>
       </c>
@@ -3380,7 +3536,7 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="57" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
         <v>75</v>
       </c>
@@ -3409,7 +3565,7 @@
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="58" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
         <v>76</v>
       </c>
@@ -3438,7 +3594,7 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="59" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
         <v>77</v>
       </c>
@@ -3467,7 +3623,7 @@
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="60" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
         <v>78</v>
       </c>
@@ -3496,7 +3652,7 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="61" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
         <v>79</v>
       </c>
@@ -3525,7 +3681,7 @@
       <c r="X61" s="3"/>
       <c r="Y61" s="3"/>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="62" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
         <v>80</v>
       </c>
@@ -3554,7 +3710,7 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="63" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
         <v>81</v>
       </c>
@@ -3583,7 +3739,7 @@
       <c r="X63" s="3"/>
       <c r="Y63" s="3"/>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="64" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
         <v>82</v>
       </c>
@@ -3612,7 +3768,7 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="65" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
         <v>83</v>
       </c>
@@ -3641,7 +3797,7 @@
       <c r="X65" s="3"/>
       <c r="Y65" s="3"/>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="66" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
         <v>84</v>
       </c>
@@ -3670,7 +3826,7 @@
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="67" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
         <v>85</v>
       </c>
@@ -3699,7 +3855,7 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="68" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
         <v>86</v>
       </c>
@@ -3728,7 +3884,7 @@
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="69" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
         <v>87</v>
       </c>
@@ -3757,7 +3913,7 @@
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="70" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
         <v>88</v>
       </c>
@@ -3786,7 +3942,7 @@
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="71" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
         <v>89</v>
       </c>
@@ -3815,7 +3971,7 @@
       <c r="X71" s="3"/>
       <c r="Y71" s="3"/>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="72" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
         <v>90</v>
       </c>
@@ -3844,7 +4000,7 @@
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="73" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
         <v>91</v>
       </c>
@@ -3873,7 +4029,7 @@
       <c r="X73" s="3"/>
       <c r="Y73" s="3"/>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="74" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
         <v>92</v>
       </c>
@@ -3902,7 +4058,7 @@
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="75" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
         <v>93</v>
       </c>
@@ -3931,7 +4087,7 @@
       <c r="X75" s="3"/>
       <c r="Y75" s="3"/>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="76" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
         <v>94</v>
       </c>
@@ -3960,7 +4116,7 @@
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="77" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
         <v>95</v>
       </c>
@@ -3989,7 +4145,7 @@
       <c r="X77" s="3"/>
       <c r="Y77" s="3"/>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="78" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
         <v>96</v>
       </c>
@@ -4018,7 +4174,7 @@
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="79" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
         <v>97</v>
       </c>
@@ -4047,20 +4203,30 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="80" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B80" s="3"/>
+      <c r="B80" s="3">
+        <v>126.31840377730295</v>
+      </c>
       <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
+      <c r="D80" s="3">
+        <v>116.20826727496747</v>
+      </c>
       <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3">
+        <v>96.531404436315427</v>
+      </c>
       <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
+      <c r="H80" s="3">
+        <v>129.06011957319154</v>
+      </c>
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
+      <c r="K80" s="3">
+        <v>148.05975191315142</v>
+      </c>
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
@@ -4068,15 +4234,19 @@
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
-      <c r="S80" s="3"/>
+      <c r="S80" s="3">
+        <v>141.15815264412834</v>
+      </c>
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
       <c r="V80" s="3"/>
-      <c r="W80" s="3"/>
+      <c r="W80" s="3">
+        <v>218.28520496307851</v>
+      </c>
       <c r="X80" s="3"/>
       <c r="Y80" s="3"/>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="81" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
         <v>99</v>
       </c>
@@ -4105,7 +4275,7 @@
       <c r="X81" s="3"/>
       <c r="Y81" s="3"/>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="82" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
         <v>100</v>
       </c>
@@ -4134,7 +4304,7 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="83" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
         <v>101</v>
       </c>
@@ -4163,36 +4333,82 @@
       <c r="X83" s="3"/>
       <c r="Y83" s="3"/>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="84" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
+      <c r="B84" s="3">
+        <v>193.14246867881983</v>
+      </c>
+      <c r="C84" s="3">
+        <v>274.00000000000006</v>
+      </c>
+      <c r="D84" s="3">
+        <v>175.39613952361802</v>
+      </c>
       <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
-      <c r="M84" s="3"/>
-      <c r="N84" s="3"/>
-      <c r="O84" s="3"/>
-      <c r="P84" s="3"/>
-      <c r="Q84" s="3"/>
-      <c r="R84" s="3"/>
-      <c r="S84" s="3"/>
-      <c r="T84" s="3"/>
-      <c r="U84" s="3"/>
-      <c r="V84" s="3"/>
-      <c r="W84" s="3"/>
-      <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="F84" s="3">
+        <v>274.00000000000006</v>
+      </c>
+      <c r="G84" s="3">
+        <v>179.2637083218801</v>
+      </c>
+      <c r="H84" s="3">
+        <v>165.89310540750185</v>
+      </c>
+      <c r="I84" s="3">
+        <v>197.61361193959934</v>
+      </c>
+      <c r="J84" s="3">
+        <v>196.4263783339552</v>
+      </c>
+      <c r="K84" s="3">
+        <v>194.96707183571249</v>
+      </c>
+      <c r="L84" s="3">
+        <v>186.60843797911773</v>
+      </c>
+      <c r="M84" s="3">
+        <v>194.18983704683552</v>
+      </c>
+      <c r="N84" s="3">
+        <v>231.93051290562076</v>
+      </c>
+      <c r="O84" s="3">
+        <v>178.04586438023992</v>
+      </c>
+      <c r="P84" s="3">
+        <v>194.66316470788928</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>195.27000987322617</v>
+      </c>
+      <c r="R84" s="3">
+        <v>194.05970943002697</v>
+      </c>
+      <c r="S84" s="3">
+        <v>191.53143095317162</v>
+      </c>
+      <c r="T84" s="3">
+        <v>220.8721347086645</v>
+      </c>
+      <c r="U84" s="3">
+        <v>188.49128263512887</v>
+      </c>
+      <c r="V84" s="3">
+        <v>188.69395588744854</v>
+      </c>
+      <c r="W84" s="3">
+        <v>193.69241674253428</v>
+      </c>
+      <c r="X84" s="3">
+        <v>193.59819466554109</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>193.14246867881983</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="85" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
         <v>103</v>
       </c>
@@ -4221,28 +4437,42 @@
       <c r="X85" s="3"/>
       <c r="Y85" s="3"/>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="86" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
+      <c r="B86" s="3">
+        <v>148.88160080103822</v>
+      </c>
+      <c r="C86" s="3">
+        <v>134.49282389246068</v>
+      </c>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
+      <c r="H86" s="3">
+        <v>150.87471985688742</v>
+      </c>
+      <c r="I86" s="3">
+        <v>123.34651894338332</v>
+      </c>
       <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
+      <c r="K86" s="3">
+        <v>133.58519002079328</v>
+      </c>
+      <c r="L86" s="3">
+        <v>148.25979425030189</v>
+      </c>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
-      <c r="S86" s="3"/>
+      <c r="S86" s="3">
+        <v>135.04334862053409</v>
+      </c>
       <c r="T86" s="3"/>
       <c r="U86" s="3"/>
       <c r="V86" s="3"/>
@@ -4250,7 +4480,7 @@
       <c r="X86" s="3"/>
       <c r="Y86" s="3"/>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="87" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
         <v>105</v>
       </c>
@@ -4279,7 +4509,7 @@
       <c r="X87" s="3"/>
       <c r="Y87" s="3"/>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="88" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
         <v>106</v>
       </c>
@@ -4308,7 +4538,7 @@
       <c r="X88" s="3"/>
       <c r="Y88" s="3"/>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="89" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
         <v>107</v>
       </c>
@@ -4337,7 +4567,7 @@
       <c r="X89" s="3"/>
       <c r="Y89" s="3"/>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="90" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
         <v>108</v>
       </c>
@@ -4366,7 +4596,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="91" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
         <v>109</v>
       </c>
@@ -4395,36 +4625,50 @@
       <c r="X91" s="3"/>
       <c r="Y91" s="3"/>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="92" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B92" s="3"/>
+      <c r="B92" s="3">
+        <v>83.73649801333282</v>
+      </c>
       <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
+      <c r="D92" s="3">
+        <v>88.663987626573629</v>
+      </c>
       <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3">
+        <v>112.53154656629012</v>
+      </c>
       <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
+      <c r="H92" s="3">
+        <v>79.622617049672513</v>
+      </c>
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
+      <c r="K92" s="3">
+        <v>46.7028569876585</v>
+      </c>
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
-      <c r="P92" s="3"/>
+      <c r="P92" s="3">
+        <v>70.955961445217099</v>
+      </c>
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
-      <c r="T92" s="3"/>
+      <c r="T92" s="3">
+        <v>65.86426737499653</v>
+      </c>
       <c r="U92" s="3"/>
       <c r="V92" s="3"/>
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="93" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
         <v>111</v>
       </c>
@@ -4453,7 +4697,7 @@
       <c r="X93" s="3"/>
       <c r="Y93" s="3"/>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="94" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
         <v>112</v>
       </c>
@@ -4482,7 +4726,7 @@
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="95" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
         <v>113</v>
       </c>
@@ -4511,7 +4755,7 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="96" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
         <v>114</v>
       </c>
@@ -4540,7 +4784,7 @@
       <c r="X96" s="3"/>
       <c r="Y96" s="3"/>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="97" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
         <v>115</v>
       </c>
@@ -4569,7 +4813,7 @@
       <c r="X97" s="3"/>
       <c r="Y97" s="3"/>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="98" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
         <v>116</v>
       </c>
@@ -4598,7 +4842,7 @@
       <c r="X98" s="3"/>
       <c r="Y98" s="3"/>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="99" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
         <v>117</v>
       </c>
@@ -4627,7 +4871,7 @@
       <c r="X99" s="3"/>
       <c r="Y99" s="3"/>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="100" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
         <v>118</v>
       </c>
@@ -4656,7 +4900,7 @@
       <c r="X100" s="3"/>
       <c r="Y100" s="3"/>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="101" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
         <v>119</v>
       </c>
@@ -4685,7 +4929,7 @@
       <c r="X101" s="3"/>
       <c r="Y101" s="3"/>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="102" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
         <v>120</v>
       </c>
@@ -4714,7 +4958,7 @@
       <c r="X102" s="3"/>
       <c r="Y102" s="3"/>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="103" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
         <v>121</v>
       </c>
@@ -4743,7 +4987,7 @@
       <c r="X103" s="3"/>
       <c r="Y103" s="3"/>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="104" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
         <v>122</v>
       </c>
@@ -4772,7 +5016,7 @@
       <c r="X104" s="3"/>
       <c r="Y104" s="3"/>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="105" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
         <v>123</v>
       </c>
@@ -4801,7 +5045,7 @@
       <c r="X105" s="3"/>
       <c r="Y105" s="3"/>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="106" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
         <v>124</v>
       </c>
@@ -4830,7 +5074,7 @@
       <c r="X106" s="3"/>
       <c r="Y106" s="3"/>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="107" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
         <v>125</v>
       </c>
@@ -4859,7 +5103,7 @@
       <c r="X107" s="3"/>
       <c r="Y107" s="3"/>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="108" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
         <v>126</v>
       </c>
@@ -4888,7 +5132,7 @@
       <c r="X108" s="3"/>
       <c r="Y108" s="3"/>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="109" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
         <v>127</v>
       </c>
@@ -4917,7 +5161,7 @@
       <c r="X109" s="3"/>
       <c r="Y109" s="3"/>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="110" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
         <v>128</v>
       </c>
@@ -4946,7 +5190,7 @@
       <c r="X110" s="3"/>
       <c r="Y110" s="3"/>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="111" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
         <v>129</v>
       </c>
@@ -4975,7 +5219,7 @@
       <c r="X111" s="3"/>
       <c r="Y111" s="3"/>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="112" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
         <v>130</v>
       </c>
@@ -5004,7 +5248,7 @@
       <c r="X112" s="3"/>
       <c r="Y112" s="3"/>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="113" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
         <v>131</v>
       </c>
@@ -5033,7 +5277,7 @@
       <c r="X113" s="3"/>
       <c r="Y113" s="3"/>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="114" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
         <v>132</v>
       </c>
@@ -5062,7 +5306,7 @@
       <c r="X114" s="3"/>
       <c r="Y114" s="3"/>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="115" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
         <v>133</v>
       </c>
@@ -5091,7 +5335,7 @@
       <c r="X115" s="3"/>
       <c r="Y115" s="3"/>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="116" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
         <v>134</v>
       </c>
@@ -5120,7 +5364,7 @@
       <c r="X116" s="3"/>
       <c r="Y116" s="3"/>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="117" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
         <v>135</v>
       </c>
@@ -5149,7 +5393,7 @@
       <c r="X117" s="3"/>
       <c r="Y117" s="3"/>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="118" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
         <v>136</v>
       </c>
@@ -5178,7 +5422,7 @@
       <c r="X118" s="3"/>
       <c r="Y118" s="3"/>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="119" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
         <v>137</v>
       </c>
@@ -5207,36 +5451,82 @@
       <c r="X119" s="3"/>
       <c r="Y119" s="3"/>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="120" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
+      <c r="B120" s="3">
+        <v>45.374204001744573</v>
+      </c>
+      <c r="C120" s="3">
+        <v>38.912154937290765</v>
+      </c>
+      <c r="D120" s="3">
+        <v>44.064486750225541</v>
+      </c>
       <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="3"/>
-      <c r="J120" s="3"/>
-      <c r="K120" s="3"/>
-      <c r="L120" s="3"/>
-      <c r="M120" s="3"/>
-      <c r="N120" s="3"/>
-      <c r="O120" s="3"/>
-      <c r="P120" s="3"/>
-      <c r="Q120" s="3"/>
-      <c r="R120" s="3"/>
-      <c r="S120" s="3"/>
-      <c r="T120" s="3"/>
-      <c r="U120" s="3"/>
-      <c r="V120" s="3"/>
-      <c r="W120" s="3"/>
-      <c r="X120" s="3"/>
-      <c r="Y120" s="3"/>
-    </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="F120" s="3">
+        <v>37.659731453383245</v>
+      </c>
+      <c r="G120" s="3">
+        <v>38.019863999539609</v>
+      </c>
+      <c r="H120" s="3">
+        <v>39.814785383699224</v>
+      </c>
+      <c r="I120" s="3">
+        <v>39.723337124672071</v>
+      </c>
+      <c r="J120" s="3">
+        <v>39.88102065482353</v>
+      </c>
+      <c r="K120" s="3">
+        <v>35.733900416382369</v>
+      </c>
+      <c r="L120" s="3">
+        <v>48.281750588699822</v>
+      </c>
+      <c r="M120" s="3">
+        <v>35.134993151385807</v>
+      </c>
+      <c r="N120" s="3">
+        <v>38.583922195730658</v>
+      </c>
+      <c r="O120" s="3">
+        <v>32.694083414991873</v>
+      </c>
+      <c r="P120" s="3">
+        <v>37.186036979303069</v>
+      </c>
+      <c r="Q120" s="3">
+        <v>57.697151117519169</v>
+      </c>
+      <c r="R120" s="3">
+        <v>38.409481832409604</v>
+      </c>
+      <c r="S120" s="3">
+        <v>33.648213914142396</v>
+      </c>
+      <c r="T120" s="3">
+        <v>37.784910754947532</v>
+      </c>
+      <c r="U120" s="3">
+        <v>38.073182832573572</v>
+      </c>
+      <c r="V120" s="3">
+        <v>35.807885545525359</v>
+      </c>
+      <c r="W120" s="3">
+        <v>35.513768117546398</v>
+      </c>
+      <c r="X120" s="3">
+        <v>33.416945982225272</v>
+      </c>
+      <c r="Y120" s="3">
+        <v>43.829975020180484</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="121" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
         <v>139</v>
       </c>
@@ -5265,7 +5555,7 @@
       <c r="X121" s="3"/>
       <c r="Y121" s="3"/>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="122" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
         <v>140</v>
       </c>
@@ -5294,7 +5584,7 @@
       <c r="X122" s="3"/>
       <c r="Y122" s="3"/>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="123" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
         <v>141</v>
       </c>
@@ -5323,7 +5613,7 @@
       <c r="X123" s="3"/>
       <c r="Y123" s="3"/>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="124" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
         <v>142</v>
       </c>
@@ -5352,7 +5642,7 @@
       <c r="X124" s="3"/>
       <c r="Y124" s="3"/>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="125" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
         <v>143</v>
       </c>
@@ -5381,7 +5671,7 @@
       <c r="X125" s="3"/>
       <c r="Y125" s="3"/>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="126" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
         <v>144</v>
       </c>
@@ -5410,7 +5700,7 @@
       <c r="X126" s="3"/>
       <c r="Y126" s="3"/>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="127" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
         <v>145</v>
       </c>
@@ -5439,7 +5729,7 @@
       <c r="X127" s="3"/>
       <c r="Y127" s="3"/>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="128" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
         <v>146</v>
       </c>
@@ -5468,36 +5758,82 @@
       <c r="X128" s="3"/>
       <c r="Y128" s="3"/>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="129" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
+      <c r="B129" s="3">
+        <v>30.000000000000004</v>
+      </c>
+      <c r="C129" s="3">
+        <v>30</v>
+      </c>
+      <c r="D129" s="3">
+        <v>28.29410289547932</v>
+      </c>
+      <c r="E129" s="3">
+        <v>29.579711819985139</v>
+      </c>
+      <c r="F129" s="3">
+        <v>28.519471661212336</v>
+      </c>
       <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
-      <c r="I129" s="3"/>
-      <c r="J129" s="3"/>
-      <c r="K129" s="3"/>
-      <c r="L129" s="3"/>
-      <c r="M129" s="3"/>
-      <c r="N129" s="3"/>
-      <c r="O129" s="3"/>
-      <c r="P129" s="3"/>
-      <c r="Q129" s="3"/>
-      <c r="R129" s="3"/>
-      <c r="S129" s="3"/>
-      <c r="T129" s="3"/>
-      <c r="U129" s="3"/>
-      <c r="V129" s="3"/>
-      <c r="W129" s="3"/>
-      <c r="X129" s="3"/>
-      <c r="Y129" s="3"/>
-    </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="H129" s="3">
+        <v>30</v>
+      </c>
+      <c r="I129" s="3">
+        <v>30</v>
+      </c>
+      <c r="J129" s="3">
+        <v>30</v>
+      </c>
+      <c r="K129" s="3">
+        <v>30</v>
+      </c>
+      <c r="L129" s="3">
+        <v>28.690868479506605</v>
+      </c>
+      <c r="M129" s="3">
+        <v>30</v>
+      </c>
+      <c r="N129" s="3">
+        <v>30</v>
+      </c>
+      <c r="O129" s="3">
+        <v>30</v>
+      </c>
+      <c r="P129" s="3">
+        <v>30</v>
+      </c>
+      <c r="Q129" s="3">
+        <v>30</v>
+      </c>
+      <c r="R129" s="3">
+        <v>30</v>
+      </c>
+      <c r="S129" s="3">
+        <v>30</v>
+      </c>
+      <c r="T129" s="3">
+        <v>30</v>
+      </c>
+      <c r="U129" s="3">
+        <v>30</v>
+      </c>
+      <c r="V129" s="3">
+        <v>29.999999999999996</v>
+      </c>
+      <c r="W129" s="3">
+        <v>29.421721059026307</v>
+      </c>
+      <c r="X129" s="3">
+        <v>27.462215754900214</v>
+      </c>
+      <c r="Y129" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="130" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
         <v>148</v>
       </c>
@@ -5526,7 +5862,7 @@
       <c r="X130" s="3"/>
       <c r="Y130" s="3"/>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="131" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
         <v>149</v>
       </c>
@@ -5555,7 +5891,7 @@
       <c r="X131" s="3"/>
       <c r="Y131" s="3"/>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="132" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
         <v>150</v>
       </c>
@@ -5584,7 +5920,7 @@
       <c r="X132" s="3"/>
       <c r="Y132" s="3"/>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="133" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
         <v>151</v>
       </c>
@@ -5613,7 +5949,7 @@
       <c r="X133" s="3"/>
       <c r="Y133" s="3"/>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="134" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
         <v>152</v>
       </c>
@@ -5642,20 +5978,26 @@
       <c r="X134" s="3"/>
       <c r="Y134" s="3"/>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="135" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B135" s="3"/>
+      <c r="B135" s="3">
+        <v>7.1821379673305961</v>
+      </c>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
-      <c r="H135" s="3"/>
+      <c r="H135" s="3">
+        <v>7.2475101720087745</v>
+      </c>
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
-      <c r="K135" s="3"/>
+      <c r="K135" s="3">
+        <v>7.3000734036452535</v>
+      </c>
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
       <c r="N135" s="3"/>
@@ -5663,15 +6005,19 @@
       <c r="P135" s="3"/>
       <c r="Q135" s="3"/>
       <c r="R135" s="3"/>
-      <c r="S135" s="3"/>
+      <c r="S135" s="3">
+        <v>6.7559304243359604</v>
+      </c>
       <c r="T135" s="3"/>
       <c r="U135" s="3"/>
       <c r="V135" s="3"/>
       <c r="W135" s="3"/>
       <c r="X135" s="3"/>
-      <c r="Y135" s="3"/>
-    </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Y135" s="3">
+        <v>6.0174570181993721</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="136" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
         <v>154</v>
       </c>
@@ -5700,7 +6046,7 @@
       <c r="X136" s="3"/>
       <c r="Y136" s="3"/>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="137" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
         <v>155</v>
       </c>
@@ -5729,7 +6075,7 @@
       <c r="X137" s="3"/>
       <c r="Y137" s="3"/>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="138" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
         <v>156</v>
       </c>
@@ -5758,7 +6104,7 @@
       <c r="X138" s="3"/>
       <c r="Y138" s="3"/>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="139" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
         <v>157</v>
       </c>
@@ -5787,7 +6133,7 @@
       <c r="X139" s="3"/>
       <c r="Y139" s="3"/>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="140" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
         <v>158</v>
       </c>
@@ -5816,7 +6162,7 @@
       <c r="X140" s="3"/>
       <c r="Y140" s="3"/>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="141" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
         <v>159</v>
       </c>
@@ -5845,7 +6191,7 @@
       <c r="X141" s="3"/>
       <c r="Y141" s="3"/>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="142" x14ac:dyDescent="0.15">
       <c r="A142" s="2" t="s">
         <v>160</v>
       </c>
@@ -5874,7 +6220,7 @@
       <c r="X142" s="3"/>
       <c r="Y142" s="3"/>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="143" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
         <v>161</v>
       </c>
@@ -5903,7 +6249,7 @@
       <c r="X143" s="3"/>
       <c r="Y143" s="3"/>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="144" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
         <v>162</v>
       </c>
@@ -5932,7 +6278,7 @@
       <c r="X144" s="3"/>
       <c r="Y144" s="3"/>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="145" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
         <v>163</v>
       </c>
@@ -5961,7 +6307,7 @@
       <c r="X145" s="3"/>
       <c r="Y145" s="3"/>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="146" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
         <v>164</v>
       </c>
@@ -5990,7 +6336,7 @@
       <c r="X146" s="3"/>
       <c r="Y146" s="3"/>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="147" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
         <v>165</v>
       </c>
@@ -6019,7 +6365,7 @@
       <c r="X147" s="3"/>
       <c r="Y147" s="3"/>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="148" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
         <v>166</v>
       </c>
@@ -6048,36 +6394,82 @@
       <c r="X148" s="3"/>
       <c r="Y148" s="3"/>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="149" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B149" s="3"/>
-      <c r="C149" s="3"/>
-      <c r="D149" s="3"/>
+      <c r="B149" s="3">
+        <v>653.54953553402333</v>
+      </c>
+      <c r="C149" s="3">
+        <v>655.18889966281415</v>
+      </c>
+      <c r="D149" s="3">
+        <v>652.44946739477143</v>
+      </c>
       <c r="E149" s="3"/>
-      <c r="F149" s="3"/>
-      <c r="G149" s="3"/>
-      <c r="H149" s="3"/>
-      <c r="I149" s="3"/>
-      <c r="J149" s="3"/>
-      <c r="K149" s="3"/>
-      <c r="L149" s="3"/>
-      <c r="M149" s="3"/>
-      <c r="N149" s="3"/>
-      <c r="O149" s="3"/>
-      <c r="P149" s="3"/>
-      <c r="Q149" s="3"/>
-      <c r="R149" s="3"/>
-      <c r="S149" s="3"/>
-      <c r="T149" s="3"/>
-      <c r="U149" s="3"/>
-      <c r="V149" s="3"/>
-      <c r="W149" s="3"/>
-      <c r="X149" s="3"/>
-      <c r="Y149" s="3"/>
-    </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="F149" s="3">
+        <v>641.95921806549154</v>
+      </c>
+      <c r="G149" s="3">
+        <v>604.09090909090901</v>
+      </c>
+      <c r="H149" s="3">
+        <v>658.94696440505049</v>
+      </c>
+      <c r="I149" s="3">
+        <v>649.70547205894195</v>
+      </c>
+      <c r="J149" s="3">
+        <v>654.46920900026362</v>
+      </c>
+      <c r="K149" s="3">
+        <v>638.36675669323995</v>
+      </c>
+      <c r="L149" s="3">
+        <v>648.62417986338153</v>
+      </c>
+      <c r="M149" s="3">
+        <v>604.09090909090901</v>
+      </c>
+      <c r="N149" s="3">
+        <v>644.04648039057929</v>
+      </c>
+      <c r="O149" s="3">
+        <v>646.55497484193234</v>
+      </c>
+      <c r="P149" s="3">
+        <v>670</v>
+      </c>
+      <c r="Q149" s="3">
+        <v>656.59375335393725</v>
+      </c>
+      <c r="R149" s="3">
+        <v>645.86077312742987</v>
+      </c>
+      <c r="S149" s="3">
+        <v>650.06448216904255</v>
+      </c>
+      <c r="T149" s="3">
+        <v>650.07285342276373</v>
+      </c>
+      <c r="U149" s="3">
+        <v>670</v>
+      </c>
+      <c r="V149" s="3">
+        <v>651.65047327975594</v>
+      </c>
+      <c r="W149" s="3">
+        <v>650.10604573335434</v>
+      </c>
+      <c r="X149" s="3">
+        <v>670</v>
+      </c>
+      <c r="Y149" s="3">
+        <v>670</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="150" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
         <v>168</v>
       </c>
@@ -6106,7 +6498,7 @@
       <c r="X150" s="3"/>
       <c r="Y150" s="3"/>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="151" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
         <v>169</v>
       </c>
@@ -6135,7 +6527,7 @@
       <c r="X151" s="3"/>
       <c r="Y151" s="3"/>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="152" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
         <v>170</v>
       </c>
@@ -6164,7 +6556,7 @@
       <c r="X152" s="3"/>
       <c r="Y152" s="3"/>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="153" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
         <v>171</v>
       </c>
@@ -6193,7 +6585,7 @@
       <c r="X153" s="3"/>
       <c r="Y153" s="3"/>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="154" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
         <v>172</v>
       </c>
@@ -6222,7 +6614,7 @@
       <c r="X154" s="3"/>
       <c r="Y154" s="3"/>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="155" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
         <v>173</v>
       </c>
@@ -6251,7 +6643,7 @@
       <c r="X155" s="3"/>
       <c r="Y155" s="3"/>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="156" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
         <v>174</v>
       </c>
@@ -6280,36 +6672,52 @@
       <c r="X156" s="3"/>
       <c r="Y156" s="3"/>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="157" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B157" s="3"/>
+      <c r="B157" s="3">
+        <v>783.27908927135218</v>
+      </c>
       <c r="C157" s="3"/>
-      <c r="D157" s="3"/>
+      <c r="D157" s="3">
+        <v>65.2314088180879</v>
+      </c>
       <c r="E157" s="3"/>
-      <c r="F157" s="3"/>
+      <c r="F157" s="3">
+        <v>786.11844807108832</v>
+      </c>
       <c r="G157" s="3"/>
-      <c r="H157" s="3"/>
-      <c r="I157" s="3"/>
+      <c r="H157" s="3">
+        <v>797.03923599131645</v>
+      </c>
+      <c r="I157" s="3">
+        <v>87.558574138528698</v>
+      </c>
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
-      <c r="L157" s="3"/>
+      <c r="L157" s="3">
+        <v>780.27385882399301</v>
+      </c>
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>
       <c r="O157" s="3"/>
       <c r="P157" s="3"/>
       <c r="Q157" s="3"/>
       <c r="R157" s="3"/>
-      <c r="S157" s="3"/>
+      <c r="S157" s="3">
+        <v>400.23604636099833</v>
+      </c>
       <c r="T157" s="3"/>
       <c r="U157" s="3"/>
-      <c r="V157" s="3"/>
+      <c r="V157" s="3">
+        <v>446.44262021310004</v>
+      </c>
       <c r="W157" s="3"/>
       <c r="X157" s="3"/>
       <c r="Y157" s="3"/>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="158" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
         <v>176</v>
       </c>
@@ -6338,7 +6746,7 @@
       <c r="X158" s="3"/>
       <c r="Y158" s="3"/>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="159" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
         <v>177</v>
       </c>
@@ -6367,36 +6775,82 @@
       <c r="X159" s="3"/>
       <c r="Y159" s="3"/>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="160" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B160" s="3"/>
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
+      <c r="B160" s="3">
+        <v>287</v>
+      </c>
+      <c r="C160" s="3">
+        <v>287</v>
+      </c>
+      <c r="D160" s="3">
+        <v>287</v>
+      </c>
       <c r="E160" s="3"/>
-      <c r="F160" s="3"/>
-      <c r="G160" s="3"/>
-      <c r="H160" s="3"/>
-      <c r="I160" s="3"/>
-      <c r="J160" s="3"/>
-      <c r="K160" s="3"/>
-      <c r="L160" s="3"/>
-      <c r="M160" s="3"/>
-      <c r="N160" s="3"/>
-      <c r="O160" s="3"/>
-      <c r="P160" s="3"/>
-      <c r="Q160" s="3"/>
-      <c r="R160" s="3"/>
-      <c r="S160" s="3"/>
-      <c r="T160" s="3"/>
-      <c r="U160" s="3"/>
-      <c r="V160" s="3"/>
-      <c r="W160" s="3"/>
-      <c r="X160" s="3"/>
-      <c r="Y160" s="3"/>
-    </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="F160" s="3">
+        <v>287</v>
+      </c>
+      <c r="G160" s="3">
+        <v>254.99771492124262</v>
+      </c>
+      <c r="H160" s="3">
+        <v>287</v>
+      </c>
+      <c r="I160" s="3">
+        <v>287</v>
+      </c>
+      <c r="J160" s="3">
+        <v>287</v>
+      </c>
+      <c r="K160" s="3">
+        <v>287</v>
+      </c>
+      <c r="L160" s="3">
+        <v>277.98580060409387</v>
+      </c>
+      <c r="M160" s="3">
+        <v>287</v>
+      </c>
+      <c r="N160" s="3">
+        <v>287</v>
+      </c>
+      <c r="O160" s="3">
+        <v>76.391699733249254</v>
+      </c>
+      <c r="P160" s="3">
+        <v>287</v>
+      </c>
+      <c r="Q160" s="3">
+        <v>284.16943674958424</v>
+      </c>
+      <c r="R160" s="3">
+        <v>287</v>
+      </c>
+      <c r="S160" s="3">
+        <v>282.97048102985184</v>
+      </c>
+      <c r="T160" s="3">
+        <v>280.95530985134502</v>
+      </c>
+      <c r="U160" s="3">
+        <v>287</v>
+      </c>
+      <c r="V160" s="3">
+        <v>251.88857163482939</v>
+      </c>
+      <c r="W160" s="3">
+        <v>261.46288808683596</v>
+      </c>
+      <c r="X160" s="3">
+        <v>287</v>
+      </c>
+      <c r="Y160" s="3">
+        <v>254.75898118401466</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="161" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
         <v>179</v>
       </c>
@@ -6425,7 +6879,7 @@
       <c r="X161" s="3"/>
       <c r="Y161" s="3"/>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="162" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
         <v>180</v>
       </c>
@@ -6454,7 +6908,7 @@
       <c r="X162" s="3"/>
       <c r="Y162" s="3"/>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="163" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
         <v>181</v>
       </c>
@@ -6483,7 +6937,7 @@
       <c r="X163" s="3"/>
       <c r="Y163" s="3"/>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="164" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
         <v>182</v>
       </c>
@@ -6512,7 +6966,7 @@
       <c r="X164" s="3"/>
       <c r="Y164" s="3"/>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="165" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
         <v>183</v>
       </c>
@@ -6541,7 +6995,7 @@
       <c r="X165" s="3"/>
       <c r="Y165" s="3"/>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="166" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
         <v>184</v>
       </c>
@@ -6570,7 +7024,7 @@
       <c r="X166" s="3"/>
       <c r="Y166" s="3"/>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="167" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
         <v>185</v>
       </c>
@@ -6599,7 +7053,7 @@
       <c r="X167" s="3"/>
       <c r="Y167" s="3"/>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="168" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
         <v>186</v>
       </c>
@@ -6628,7 +7082,7 @@
       <c r="X168" s="3"/>
       <c r="Y168" s="3"/>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="169" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
         <v>187</v>
       </c>
@@ -6657,7 +7111,7 @@
       <c r="X169" s="3"/>
       <c r="Y169" s="3"/>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="170" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
         <v>188</v>
       </c>
@@ -6686,7 +7140,7 @@
       <c r="X170" s="3"/>
       <c r="Y170" s="3"/>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="171" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
         <v>189</v>
       </c>
@@ -6715,7 +7169,7 @@
       <c r="X171" s="3"/>
       <c r="Y171" s="3"/>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="172" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
         <v>190</v>
       </c>
@@ -6744,7 +7198,7 @@
       <c r="X172" s="3"/>
       <c r="Y172" s="3"/>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="173" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
         <v>191</v>
       </c>
@@ -6773,7 +7227,7 @@
       <c r="X173" s="3"/>
       <c r="Y173" s="3"/>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="174" x14ac:dyDescent="0.15">
       <c r="A174" s="2" t="s">
         <v>192</v>
       </c>
@@ -6802,7 +7256,7 @@
       <c r="X174" s="3"/>
       <c r="Y174" s="3"/>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="175" x14ac:dyDescent="0.15">
       <c r="A175" s="2" t="s">
         <v>193</v>
       </c>
@@ -6831,7 +7285,7 @@
       <c r="X175" s="3"/>
       <c r="Y175" s="3"/>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="176" x14ac:dyDescent="0.15">
       <c r="A176" s="2" t="s">
         <v>194</v>
       </c>
@@ -6860,7 +7314,7 @@
       <c r="X176" s="3"/>
       <c r="Y176" s="3"/>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="177" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
         <v>195</v>
       </c>
@@ -6889,7 +7343,7 @@
       <c r="X177" s="3"/>
       <c r="Y177" s="3"/>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="178" x14ac:dyDescent="0.15">
       <c r="A178" s="2" t="s">
         <v>196</v>
       </c>
@@ -6918,7 +7372,7 @@
       <c r="X178" s="3"/>
       <c r="Y178" s="3"/>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="179" x14ac:dyDescent="0.15">
       <c r="A179" s="2" t="s">
         <v>197</v>
       </c>
@@ -6947,7 +7401,7 @@
       <c r="X179" s="3"/>
       <c r="Y179" s="3"/>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="180" x14ac:dyDescent="0.15">
       <c r="A180" s="2" t="s">
         <v>198</v>
       </c>
@@ -6976,7 +7430,7 @@
       <c r="X180" s="3"/>
       <c r="Y180" s="3"/>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="181" x14ac:dyDescent="0.15">
       <c r="A181" s="2" t="s">
         <v>199</v>
       </c>
@@ -7005,7 +7459,7 @@
       <c r="X181" s="3"/>
       <c r="Y181" s="3"/>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="182" x14ac:dyDescent="0.15">
       <c r="A182" s="2" t="s">
         <v>200</v>
       </c>
@@ -7034,7 +7488,7 @@
       <c r="X182" s="3"/>
       <c r="Y182" s="3"/>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="183" x14ac:dyDescent="0.15">
       <c r="A183" s="2" t="s">
         <v>201</v>
       </c>
@@ -7063,7 +7517,7 @@
       <c r="X183" s="3"/>
       <c r="Y183" s="3"/>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="184" x14ac:dyDescent="0.15">
       <c r="A184" s="2" t="s">
         <v>202</v>
       </c>
@@ -7092,7 +7546,7 @@
       <c r="X184" s="3"/>
       <c r="Y184" s="3"/>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="185" x14ac:dyDescent="0.15">
       <c r="A185" s="2" t="s">
         <v>203</v>
       </c>
@@ -7121,7 +7575,7 @@
       <c r="X185" s="3"/>
       <c r="Y185" s="3"/>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="186" x14ac:dyDescent="0.15">
       <c r="A186" s="2" t="s">
         <v>204</v>
       </c>
@@ -7150,7 +7604,7 @@
       <c r="X186" s="3"/>
       <c r="Y186" s="3"/>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="187" x14ac:dyDescent="0.15">
       <c r="A187" s="2" t="s">
         <v>205</v>
       </c>
@@ -7179,7 +7633,7 @@
       <c r="X187" s="3"/>
       <c r="Y187" s="3"/>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="188" x14ac:dyDescent="0.15">
       <c r="A188" s="2" t="s">
         <v>206</v>
       </c>
@@ -7208,7 +7662,7 @@
       <c r="X188" s="3"/>
       <c r="Y188" s="3"/>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="189" x14ac:dyDescent="0.15">
       <c r="A189" s="2" t="s">
         <v>207</v>
       </c>
@@ -7237,7 +7691,7 @@
       <c r="X189" s="3"/>
       <c r="Y189" s="3"/>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="190" x14ac:dyDescent="0.15">
       <c r="A190" s="2" t="s">
         <v>208</v>
       </c>
@@ -7266,7 +7720,7 @@
       <c r="X190" s="3"/>
       <c r="Y190" s="3"/>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="191" x14ac:dyDescent="0.15">
       <c r="A191" s="2" t="s">
         <v>209</v>
       </c>
@@ -7295,7 +7749,7 @@
       <c r="X191" s="3"/>
       <c r="Y191" s="3"/>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="192" x14ac:dyDescent="0.15">
       <c r="A192" s="2" t="s">
         <v>210</v>
       </c>
@@ -7324,7 +7778,7 @@
       <c r="X192" s="3"/>
       <c r="Y192" s="3"/>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="193" x14ac:dyDescent="0.15">
       <c r="A193" s="2" t="s">
         <v>211</v>
       </c>
@@ -7353,7 +7807,7 @@
       <c r="X193" s="3"/>
       <c r="Y193" s="3"/>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="194" x14ac:dyDescent="0.15">
       <c r="A194" s="2" t="s">
         <v>212</v>
       </c>
@@ -7382,7 +7836,7 @@
       <c r="X194" s="3"/>
       <c r="Y194" s="3"/>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="195" x14ac:dyDescent="0.15">
       <c r="A195" s="2" t="s">
         <v>213</v>
       </c>
@@ -7411,7 +7865,7 @@
       <c r="X195" s="3"/>
       <c r="Y195" s="3"/>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="196" x14ac:dyDescent="0.15">
       <c r="A196" s="2" t="s">
         <v>214</v>
       </c>
@@ -7440,7 +7894,7 @@
       <c r="X196" s="3"/>
       <c r="Y196" s="3"/>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="197" x14ac:dyDescent="0.15">
       <c r="A197" s="2" t="s">
         <v>215</v>
       </c>
@@ -7469,7 +7923,7 @@
       <c r="X197" s="3"/>
       <c r="Y197" s="3"/>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="198" x14ac:dyDescent="0.15">
       <c r="A198" s="2" t="s">
         <v>216</v>
       </c>
@@ -7498,7 +7952,7 @@
       <c r="X198" s="3"/>
       <c r="Y198" s="3"/>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="199" x14ac:dyDescent="0.15">
       <c r="A199" s="2" t="s">
         <v>217</v>
       </c>
@@ -7527,36 +7981,52 @@
       <c r="X199" s="3"/>
       <c r="Y199" s="3"/>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="200" x14ac:dyDescent="0.15">
       <c r="A200" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B200" s="3"/>
+      <c r="B200" s="3">
+        <v>493.04862077291119</v>
+      </c>
       <c r="C200" s="3"/>
-      <c r="D200" s="3"/>
+      <c r="D200" s="3">
+        <v>500</v>
+      </c>
       <c r="E200" s="3"/>
-      <c r="F200" s="3"/>
+      <c r="F200" s="3">
+        <v>493.40488531566342</v>
+      </c>
       <c r="G200" s="3"/>
-      <c r="H200" s="3"/>
+      <c r="H200" s="3">
+        <v>495.56306641663377</v>
+      </c>
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
-      <c r="K200" s="3"/>
+      <c r="K200" s="3">
+        <v>493.65297227808418</v>
+      </c>
       <c r="L200" s="3"/>
-      <c r="M200" s="3"/>
+      <c r="M200" s="3">
+        <v>451.44855665013802</v>
+      </c>
       <c r="N200" s="3"/>
       <c r="O200" s="3"/>
       <c r="P200" s="3"/>
       <c r="Q200" s="3"/>
       <c r="R200" s="3"/>
-      <c r="S200" s="3"/>
-      <c r="T200" s="3"/>
+      <c r="S200" s="3">
+        <v>495.65277207503965</v>
+      </c>
+      <c r="T200" s="3">
+        <v>499.25463098999438</v>
+      </c>
       <c r="U200" s="3"/>
       <c r="V200" s="3"/>
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
       <c r="Y200" s="3"/>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="201" x14ac:dyDescent="0.15">
       <c r="A201" s="2" t="s">
         <v>219</v>
       </c>
@@ -7585,7 +8055,7 @@
       <c r="X201" s="3"/>
       <c r="Y201" s="3"/>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="202" x14ac:dyDescent="0.15">
       <c r="A202" s="2" t="s">
         <v>220</v>
       </c>
@@ -7614,7 +8084,7 @@
       <c r="X202" s="3"/>
       <c r="Y202" s="3"/>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="203" x14ac:dyDescent="0.15">
       <c r="A203" s="2" t="s">
         <v>221</v>
       </c>
@@ -7643,7 +8113,7 @@
       <c r="X203" s="3"/>
       <c r="Y203" s="3"/>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="204" x14ac:dyDescent="0.15">
       <c r="A204" s="2" t="s">
         <v>222</v>
       </c>
@@ -7672,7 +8142,7 @@
       <c r="X204" s="3"/>
       <c r="Y204" s="3"/>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="205" x14ac:dyDescent="0.15">
       <c r="A205" s="2" t="s">
         <v>223</v>
       </c>
@@ -7701,7 +8171,7 @@
       <c r="X205" s="3"/>
       <c r="Y205" s="3"/>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="206" x14ac:dyDescent="0.15">
       <c r="A206" s="2" t="s">
         <v>224</v>
       </c>
@@ -7730,36 +8200,84 @@
       <c r="X206" s="3"/>
       <c r="Y206" s="3"/>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="207" x14ac:dyDescent="0.15">
       <c r="A207" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B207" s="3"/>
-      <c r="C207" s="3"/>
-      <c r="D207" s="3"/>
-      <c r="E207" s="3"/>
-      <c r="F207" s="3"/>
-      <c r="G207" s="3"/>
-      <c r="H207" s="3"/>
-      <c r="I207" s="3"/>
-      <c r="J207" s="3"/>
-      <c r="K207" s="3"/>
-      <c r="L207" s="3"/>
-      <c r="M207" s="3"/>
-      <c r="N207" s="3"/>
-      <c r="O207" s="3"/>
-      <c r="P207" s="3"/>
-      <c r="Q207" s="3"/>
-      <c r="R207" s="3"/>
-      <c r="S207" s="3"/>
-      <c r="T207" s="3"/>
-      <c r="U207" s="3"/>
-      <c r="V207" s="3"/>
-      <c r="W207" s="3"/>
-      <c r="X207" s="3"/>
-      <c r="Y207" s="3"/>
-    </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B207" s="3">
+        <v>6613.1638330238147</v>
+      </c>
+      <c r="C207" s="3">
+        <v>12922.833956245991</v>
+      </c>
+      <c r="D207" s="3">
+        <v>12922.833956245991</v>
+      </c>
+      <c r="E207" s="3">
+        <v>8615.2226374973288</v>
+      </c>
+      <c r="F207" s="3">
+        <v>12922.833956245991</v>
+      </c>
+      <c r="G207" s="3">
+        <v>1963.7642055047249</v>
+      </c>
+      <c r="H207" s="3">
+        <v>12922.833956245991</v>
+      </c>
+      <c r="I207" s="3">
+        <v>12922.833956245991</v>
+      </c>
+      <c r="J207" s="3">
+        <v>8615.2226374973288</v>
+      </c>
+      <c r="K207" s="3">
+        <v>12922.833956245991</v>
+      </c>
+      <c r="L207" s="3">
+        <v>6713.2345145997615</v>
+      </c>
+      <c r="M207" s="3">
+        <v>8615.2226374973288</v>
+      </c>
+      <c r="N207" s="3">
+        <v>3639.0096813880337</v>
+      </c>
+      <c r="O207" s="3">
+        <v>12922.833956245991</v>
+      </c>
+      <c r="P207" s="3">
+        <v>6639.306501969234</v>
+      </c>
+      <c r="Q207" s="3">
+        <v>12564.159453625796</v>
+      </c>
+      <c r="R207" s="3">
+        <v>6708.4649536130382</v>
+      </c>
+      <c r="S207" s="3">
+        <v>6714.2839654584595</v>
+      </c>
+      <c r="T207" s="3">
+        <v>7844.102118495206</v>
+      </c>
+      <c r="U207" s="3">
+        <v>2536.9160723246673</v>
+      </c>
+      <c r="V207" s="3">
+        <v>11782.62119009215</v>
+      </c>
+      <c r="W207" s="3">
+        <v>13157.508395259532</v>
+      </c>
+      <c r="X207" s="3">
+        <v>6716.5625608441333</v>
+      </c>
+      <c r="Y207" s="3">
+        <v>8615.2226374973288</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="208" x14ac:dyDescent="0.15">
       <c r="A208" s="2" t="s">
         <v>226</v>
       </c>
@@ -7788,7 +8306,7 @@
       <c r="X208" s="3"/>
       <c r="Y208" s="3"/>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="209" x14ac:dyDescent="0.15">
       <c r="A209" s="2" t="s">
         <v>227</v>
       </c>
@@ -7817,7 +8335,7 @@
       <c r="X209" s="3"/>
       <c r="Y209" s="3"/>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="210" x14ac:dyDescent="0.15">
       <c r="A210" s="2" t="s">
         <v>228</v>
       </c>
@@ -7846,7 +8364,7 @@
       <c r="X210" s="3"/>
       <c r="Y210" s="3"/>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="211" x14ac:dyDescent="0.15">
       <c r="A211" s="2" t="s">
         <v>229</v>
       </c>
@@ -7875,7 +8393,7 @@
       <c r="X211" s="3"/>
       <c r="Y211" s="3"/>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="212" x14ac:dyDescent="0.15">
       <c r="A212" s="2" t="s">
         <v>230</v>
       </c>
@@ -7904,7 +8422,7 @@
       <c r="X212" s="3"/>
       <c r="Y212" s="3"/>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="213" x14ac:dyDescent="0.15">
       <c r="A213" s="2" t="s">
         <v>231</v>
       </c>
@@ -7933,7 +8451,7 @@
       <c r="X213" s="3"/>
       <c r="Y213" s="3"/>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="214" x14ac:dyDescent="0.15">
       <c r="A214" s="2" t="s">
         <v>232</v>
       </c>
@@ -7962,7 +8480,7 @@
       <c r="X214" s="3"/>
       <c r="Y214" s="3"/>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="215" x14ac:dyDescent="0.15">
       <c r="A215" s="2" t="s">
         <v>233</v>
       </c>
@@ -7991,36 +8509,52 @@
       <c r="X215" s="3"/>
       <c r="Y215" s="3"/>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="216" x14ac:dyDescent="0.15">
       <c r="A216" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B216" s="3"/>
+      <c r="B216" s="3">
+        <v>519.43176241902745</v>
+      </c>
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
-      <c r="F216" s="3"/>
+      <c r="F216" s="3">
+        <v>527.48515486127838</v>
+      </c>
       <c r="G216" s="3"/>
-      <c r="H216" s="3"/>
+      <c r="H216" s="3">
+        <v>421.46866395287066</v>
+      </c>
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
-      <c r="K216" s="3"/>
+      <c r="K216" s="3">
+        <v>381.15193051353515</v>
+      </c>
       <c r="L216" s="3"/>
-      <c r="M216" s="3"/>
+      <c r="M216" s="3">
+        <v>767.05913745724865</v>
+      </c>
       <c r="N216" s="3"/>
       <c r="O216" s="3"/>
-      <c r="P216" s="3"/>
+      <c r="P216" s="3">
+        <v>522.44529111361123</v>
+      </c>
       <c r="Q216" s="3"/>
       <c r="R216" s="3"/>
-      <c r="S216" s="3"/>
+      <c r="S216" s="3">
+        <v>416.22085204186499</v>
+      </c>
       <c r="T216" s="3"/>
       <c r="U216" s="3"/>
       <c r="V216" s="3"/>
-      <c r="W216" s="3"/>
+      <c r="W216" s="3">
+        <v>472.83538686386811</v>
+      </c>
       <c r="X216" s="3"/>
       <c r="Y216" s="3"/>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="217" x14ac:dyDescent="0.15">
       <c r="A217" s="2" t="s">
         <v>235</v>
       </c>
@@ -8049,7 +8583,7 @@
       <c r="X217" s="3"/>
       <c r="Y217" s="3"/>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="218" x14ac:dyDescent="0.15">
       <c r="A218" s="2" t="s">
         <v>236</v>
       </c>
@@ -8078,7 +8612,7 @@
       <c r="X218" s="3"/>
       <c r="Y218" s="3"/>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="219" x14ac:dyDescent="0.15">
       <c r="A219" s="2" t="s">
         <v>237</v>
       </c>
@@ -8107,7 +8641,7 @@
       <c r="X219" s="3"/>
       <c r="Y219" s="3"/>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="220" x14ac:dyDescent="0.15">
       <c r="A220" s="2" t="s">
         <v>238</v>
       </c>
@@ -8136,7 +8670,7 @@
       <c r="X220" s="3"/>
       <c r="Y220" s="3"/>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="221" x14ac:dyDescent="0.15">
       <c r="A221" s="2" t="s">
         <v>239</v>
       </c>
@@ -8165,7 +8699,7 @@
       <c r="X221" s="3"/>
       <c r="Y221" s="3"/>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="222" x14ac:dyDescent="0.15">
       <c r="A222" s="2" t="s">
         <v>240</v>
       </c>
@@ -8194,7 +8728,7 @@
       <c r="X222" s="3"/>
       <c r="Y222" s="3"/>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="223" x14ac:dyDescent="0.15">
       <c r="A223" s="2" t="s">
         <v>241</v>
       </c>
@@ -8223,20 +8757,30 @@
       <c r="X223" s="3"/>
       <c r="Y223" s="3"/>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="224" x14ac:dyDescent="0.15">
       <c r="A224" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B224" s="3"/>
-      <c r="C224" s="3"/>
-      <c r="D224" s="3"/>
+      <c r="B224" s="3">
+        <v>110</v>
+      </c>
+      <c r="C224" s="3">
+        <v>92.306207202756227</v>
+      </c>
+      <c r="D224" s="3">
+        <v>110</v>
+      </c>
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
       <c r="G224" s="3"/>
       <c r="H224" s="3"/>
-      <c r="I224" s="3"/>
+      <c r="I224" s="3">
+        <v>103.81872357751102</v>
+      </c>
       <c r="J224" s="3"/>
-      <c r="K224" s="3"/>
+      <c r="K224" s="3">
+        <v>96.55140532652915</v>
+      </c>
       <c r="L224" s="3"/>
       <c r="M224" s="3"/>
       <c r="N224" s="3"/>
@@ -8244,15 +8788,19 @@
       <c r="P224" s="3"/>
       <c r="Q224" s="3"/>
       <c r="R224" s="3"/>
-      <c r="S224" s="3"/>
-      <c r="T224" s="3"/>
+      <c r="S224" s="3">
+        <v>101.31364086570018</v>
+      </c>
+      <c r="T224" s="3">
+        <v>108.16963783787163</v>
+      </c>
       <c r="U224" s="3"/>
       <c r="V224" s="3"/>
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="3"/>
     </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="225" x14ac:dyDescent="0.15">
       <c r="A225" s="2" t="s">
         <v>243</v>
       </c>
@@ -8281,7 +8829,7 @@
       <c r="X225" s="3"/>
       <c r="Y225" s="3"/>
     </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="226" x14ac:dyDescent="0.15">
       <c r="A226" s="2" t="s">
         <v>244</v>
       </c>
@@ -8310,7 +8858,7 @@
       <c r="X226" s="3"/>
       <c r="Y226" s="3"/>
     </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="227" x14ac:dyDescent="0.15">
       <c r="A227" s="2" t="s">
         <v>245</v>
       </c>
@@ -8339,7 +8887,7 @@
       <c r="X227" s="3"/>
       <c r="Y227" s="3"/>
     </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="228" x14ac:dyDescent="0.15">
       <c r="A228" s="2" t="s">
         <v>246</v>
       </c>
@@ -8368,7 +8916,7 @@
       <c r="X228" s="3"/>
       <c r="Y228" s="3"/>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="229" x14ac:dyDescent="0.15">
       <c r="A229" s="2" t="s">
         <v>247</v>
       </c>
@@ -8397,7 +8945,7 @@
       <c r="X229" s="3"/>
       <c r="Y229" s="3"/>
     </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="230" x14ac:dyDescent="0.15">
       <c r="A230" s="2" t="s">
         <v>248</v>
       </c>
@@ -8426,7 +8974,7 @@
       <c r="X230" s="3"/>
       <c r="Y230" s="3"/>
     </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="231" x14ac:dyDescent="0.15">
       <c r="A231" s="2" t="s">
         <v>249</v>
       </c>
@@ -8455,7 +9003,7 @@
       <c r="X231" s="3"/>
       <c r="Y231" s="3"/>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="232" x14ac:dyDescent="0.15">
       <c r="A232" s="2" t="s">
         <v>250</v>
       </c>
@@ -8484,7 +9032,7 @@
       <c r="X232" s="3"/>
       <c r="Y232" s="3"/>
     </row>
-    <row r="233" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="233" x14ac:dyDescent="0.15">
       <c r="A233" s="2" t="s">
         <v>251</v>
       </c>
@@ -8513,7 +9061,7 @@
       <c r="X233" s="3"/>
       <c r="Y233" s="3"/>
     </row>
-    <row r="234" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="234" x14ac:dyDescent="0.15">
       <c r="A234" s="2" t="s">
         <v>252</v>
       </c>
@@ -8542,36 +9090,82 @@
       <c r="X234" s="3"/>
       <c r="Y234" s="3"/>
     </row>
-    <row r="235" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="235" x14ac:dyDescent="0.15">
       <c r="A235" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B235" s="3"/>
-      <c r="C235" s="3"/>
-      <c r="D235" s="3"/>
-      <c r="E235" s="3"/>
-      <c r="F235" s="3"/>
+      <c r="B235" s="3">
+        <v>2063.9172543670529</v>
+      </c>
+      <c r="C235" s="3">
+        <v>2057.1833688336528</v>
+      </c>
+      <c r="D235" s="3">
+        <v>2063.1469122831986</v>
+      </c>
+      <c r="E235" s="3">
+        <v>2070.578753210832</v>
+      </c>
+      <c r="F235" s="3">
+        <v>2059.3005322898625</v>
+      </c>
       <c r="G235" s="3"/>
-      <c r="H235" s="3"/>
-      <c r="I235" s="3"/>
-      <c r="J235" s="3"/>
-      <c r="K235" s="3"/>
-      <c r="L235" s="3"/>
-      <c r="M235" s="3"/>
-      <c r="N235" s="3"/>
-      <c r="O235" s="3"/>
-      <c r="P235" s="3"/>
-      <c r="Q235" s="3"/>
-      <c r="R235" s="3"/>
-      <c r="S235" s="3"/>
-      <c r="T235" s="3"/>
-      <c r="U235" s="3"/>
-      <c r="V235" s="3"/>
-      <c r="W235" s="3"/>
-      <c r="X235" s="3"/>
-      <c r="Y235" s="3"/>
-    </row>
-    <row r="236" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="H235" s="3">
+        <v>2131</v>
+      </c>
+      <c r="I235" s="3">
+        <v>2067.8277896040599</v>
+      </c>
+      <c r="J235" s="3">
+        <v>2062.070003593909</v>
+      </c>
+      <c r="K235" s="3">
+        <v>2073.8497038801979</v>
+      </c>
+      <c r="L235" s="3">
+        <v>2131</v>
+      </c>
+      <c r="M235" s="3">
+        <v>2061.4273199590011</v>
+      </c>
+      <c r="N235" s="3">
+        <v>2067.1253233278276</v>
+      </c>
+      <c r="O235" s="3">
+        <v>2131</v>
+      </c>
+      <c r="P235" s="3">
+        <v>2062.2478505612698</v>
+      </c>
+      <c r="Q235" s="3">
+        <v>2060.4212782582099</v>
+      </c>
+      <c r="R235" s="3">
+        <v>2057.1930591987789</v>
+      </c>
+      <c r="S235" s="3">
+        <v>2056.7559522532042</v>
+      </c>
+      <c r="T235" s="3">
+        <v>2063.5665946530107</v>
+      </c>
+      <c r="U235" s="3">
+        <v>2058.4242106470115</v>
+      </c>
+      <c r="V235" s="3">
+        <v>2062.2307635251032</v>
+      </c>
+      <c r="W235" s="3">
+        <v>2064.9189088927073</v>
+      </c>
+      <c r="X235" s="3">
+        <v>2058.0017230734352</v>
+      </c>
+      <c r="Y235" s="3">
+        <v>2076.2975238604195</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="236" x14ac:dyDescent="0.15">
       <c r="A236" s="2" t="s">
         <v>254</v>
       </c>
@@ -8600,7 +9194,7 @@
       <c r="X236" s="3"/>
       <c r="Y236" s="3"/>
     </row>
-    <row r="237" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="237" x14ac:dyDescent="0.15">
       <c r="A237" s="2" t="s">
         <v>255</v>
       </c>
@@ -8629,7 +9223,7 @@
       <c r="X237" s="3"/>
       <c r="Y237" s="3"/>
     </row>
-    <row r="238" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="238" x14ac:dyDescent="0.15">
       <c r="A238" s="2" t="s">
         <v>256</v>
       </c>
@@ -8658,7 +9252,7 @@
       <c r="X238" s="3"/>
       <c r="Y238" s="3"/>
     </row>
-    <row r="239" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="239" x14ac:dyDescent="0.15">
       <c r="A239" s="2" t="s">
         <v>257</v>
       </c>
@@ -8687,7 +9281,7 @@
       <c r="X239" s="3"/>
       <c r="Y239" s="3"/>
     </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="240" x14ac:dyDescent="0.15">
       <c r="A240" s="2" t="s">
         <v>258</v>
       </c>
@@ -8716,7 +9310,7 @@
       <c r="X240" s="3"/>
       <c r="Y240" s="3"/>
     </row>
-    <row r="241" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="241" x14ac:dyDescent="0.15">
       <c r="A241" s="2" t="s">
         <v>259</v>
       </c>
@@ -8745,7 +9339,7 @@
       <c r="X241" s="3"/>
       <c r="Y241" s="3"/>
     </row>
-    <row r="242" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="242" x14ac:dyDescent="0.15">
       <c r="A242" s="2" t="s">
         <v>260</v>
       </c>
@@ -8774,7 +9368,7 @@
       <c r="X242" s="3"/>
       <c r="Y242" s="3"/>
     </row>
-    <row r="243" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="243" x14ac:dyDescent="0.15">
       <c r="A243" s="2" t="s">
         <v>261</v>
       </c>
@@ -8803,7 +9397,7 @@
       <c r="X243" s="3"/>
       <c r="Y243" s="3"/>
     </row>
-    <row r="244" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="244" x14ac:dyDescent="0.15">
       <c r="A244" s="2" t="s">
         <v>262</v>
       </c>
@@ -8832,7 +9426,7 @@
       <c r="X244" s="3"/>
       <c r="Y244" s="3"/>
     </row>
-    <row r="245" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="245" x14ac:dyDescent="0.15">
       <c r="A245" s="2" t="s">
         <v>263</v>
       </c>
@@ -8861,7 +9455,7 @@
       <c r="X245" s="3"/>
       <c r="Y245" s="3"/>
     </row>
-    <row r="246" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="246" x14ac:dyDescent="0.15">
       <c r="A246" s="2" t="s">
         <v>264</v>
       </c>
@@ -8890,7 +9484,7 @@
       <c r="X246" s="3"/>
       <c r="Y246" s="3"/>
     </row>
-    <row r="247" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="247" x14ac:dyDescent="0.15">
       <c r="A247" s="2" t="s">
         <v>265</v>
       </c>
@@ -8919,7 +9513,7 @@
       <c r="X247" s="3"/>
       <c r="Y247" s="3"/>
     </row>
-    <row r="248" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="248" x14ac:dyDescent="0.15">
       <c r="A248" s="2" t="s">
         <v>266</v>
       </c>
@@ -8948,7 +9542,7 @@
       <c r="X248" s="3"/>
       <c r="Y248" s="3"/>
     </row>
-    <row r="249" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="249" x14ac:dyDescent="0.15">
       <c r="A249" s="2" t="s">
         <v>267</v>
       </c>
@@ -8977,36 +9571,50 @@
       <c r="X249" s="3"/>
       <c r="Y249" s="3"/>
     </row>
-    <row r="250" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="250" x14ac:dyDescent="0.15">
       <c r="A250" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B250" s="3"/>
+      <c r="B250" s="3">
+        <v>108.75269993412675</v>
+      </c>
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
       <c r="G250" s="3"/>
-      <c r="H250" s="3"/>
-      <c r="I250" s="3"/>
+      <c r="H250" s="3">
+        <v>108.36567007531356</v>
+      </c>
+      <c r="I250" s="3">
+        <v>109.24622457434781</v>
+      </c>
       <c r="J250" s="3"/>
-      <c r="K250" s="3"/>
+      <c r="K250" s="3">
+        <v>111.39314291770444</v>
+      </c>
       <c r="L250" s="3"/>
       <c r="M250" s="3"/>
       <c r="N250" s="3"/>
       <c r="O250" s="3"/>
-      <c r="P250" s="3"/>
+      <c r="P250" s="3">
+        <v>111.19943185031106</v>
+      </c>
       <c r="Q250" s="3"/>
       <c r="R250" s="3"/>
       <c r="S250" s="3"/>
-      <c r="T250" s="3"/>
+      <c r="T250" s="3">
+        <v>113.7883125631526</v>
+      </c>
       <c r="U250" s="3"/>
       <c r="V250" s="3"/>
       <c r="W250" s="3"/>
       <c r="X250" s="3"/>
-      <c r="Y250" s="3"/>
-    </row>
-    <row r="251" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Y250" s="3">
+        <v>114.46456700182588</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="251" x14ac:dyDescent="0.15">
       <c r="A251" s="2" t="s">
         <v>269</v>
       </c>
@@ -9035,7 +9643,7 @@
       <c r="X251" s="3"/>
       <c r="Y251" s="3"/>
     </row>
-    <row r="252" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="252" x14ac:dyDescent="0.15">
       <c r="A252" s="2" t="s">
         <v>270</v>
       </c>
@@ -9064,36 +9672,50 @@
       <c r="X252" s="3"/>
       <c r="Y252" s="3"/>
     </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="253" x14ac:dyDescent="0.15">
       <c r="A253" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B253" s="3"/>
+      <c r="B253" s="3">
+        <v>275.16294906982415</v>
+      </c>
       <c r="C253" s="3"/>
-      <c r="D253" s="3"/>
+      <c r="D253" s="3">
+        <v>280</v>
+      </c>
       <c r="E253" s="3"/>
-      <c r="F253" s="3"/>
+      <c r="F253" s="3">
+        <v>276.44461247412318</v>
+      </c>
       <c r="G253" s="3"/>
-      <c r="H253" s="3"/>
+      <c r="H253" s="3">
+        <v>275.62001363702149</v>
+      </c>
       <c r="I253" s="3"/>
       <c r="J253" s="3"/>
-      <c r="K253" s="3"/>
+      <c r="K253" s="3">
+        <v>274.8027359364192</v>
+      </c>
       <c r="L253" s="3"/>
       <c r="M253" s="3"/>
       <c r="N253" s="3"/>
       <c r="O253" s="3"/>
-      <c r="P253" s="3"/>
+      <c r="P253" s="3">
+        <v>274.12977507759052</v>
+      </c>
       <c r="Q253" s="3"/>
       <c r="R253" s="3"/>
       <c r="S253" s="3"/>
       <c r="T253" s="3"/>
       <c r="U253" s="3"/>
-      <c r="V253" s="3"/>
+      <c r="V253" s="3">
+        <v>277.73654276749204</v>
+      </c>
       <c r="W253" s="3"/>
       <c r="X253" s="3"/>
       <c r="Y253" s="3"/>
     </row>
-    <row r="254" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="254" x14ac:dyDescent="0.15">
       <c r="A254" s="2" t="s">
         <v>272</v>
       </c>
@@ -9122,7 +9744,7 @@
       <c r="X254" s="3"/>
       <c r="Y254" s="3"/>
     </row>
-    <row r="255" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="255" x14ac:dyDescent="0.15">
       <c r="A255" s="2" t="s">
         <v>273</v>
       </c>
@@ -9151,7 +9773,7 @@
       <c r="X255" s="3"/>
       <c r="Y255" s="3"/>
     </row>
-    <row r="256" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="256" x14ac:dyDescent="0.15">
       <c r="A256" s="2" t="s">
         <v>274</v>
       </c>
@@ -9180,7 +9802,7 @@
       <c r="X256" s="3"/>
       <c r="Y256" s="3"/>
     </row>
-    <row r="257" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="257" x14ac:dyDescent="0.15">
       <c r="A257" s="2" t="s">
         <v>275</v>
       </c>
@@ -9209,7 +9831,7 @@
       <c r="X257" s="3"/>
       <c r="Y257" s="3"/>
     </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="258" x14ac:dyDescent="0.15">
       <c r="A258" s="2" t="s">
         <v>276</v>
       </c>
@@ -9238,7 +9860,7 @@
       <c r="X258" s="3"/>
       <c r="Y258" s="3"/>
     </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="259" x14ac:dyDescent="0.15">
       <c r="A259" s="2" t="s">
         <v>277</v>
       </c>
@@ -9267,7 +9889,7 @@
       <c r="X259" s="3"/>
       <c r="Y259" s="3"/>
     </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="260" x14ac:dyDescent="0.15">
       <c r="A260" s="2" t="s">
         <v>278</v>
       </c>
@@ -9296,7 +9918,7 @@
       <c r="X260" s="3"/>
       <c r="Y260" s="3"/>
     </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="261" x14ac:dyDescent="0.15">
       <c r="A261" s="2" t="s">
         <v>279</v>
       </c>
@@ -9325,7 +9947,7 @@
       <c r="X261" s="3"/>
       <c r="Y261" s="3"/>
     </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="262" x14ac:dyDescent="0.15">
       <c r="A262" s="2" t="s">
         <v>280</v>
       </c>
@@ -9354,7 +9976,7 @@
       <c r="X262" s="3"/>
       <c r="Y262" s="3"/>
     </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="263" x14ac:dyDescent="0.15">
       <c r="A263" s="2" t="s">
         <v>281</v>
       </c>
@@ -9383,7 +10005,7 @@
       <c r="X263" s="3"/>
       <c r="Y263" s="3"/>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="264" x14ac:dyDescent="0.15">
       <c r="A264" s="2" t="s">
         <v>282</v>
       </c>
@@ -9412,7 +10034,7 @@
       <c r="X264" s="3"/>
       <c r="Y264" s="3"/>
     </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="265" x14ac:dyDescent="0.15">
       <c r="A265" s="2" t="s">
         <v>283</v>
       </c>
@@ -9441,7 +10063,7 @@
       <c r="X265" s="3"/>
       <c r="Y265" s="3"/>
     </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="266" x14ac:dyDescent="0.15">
       <c r="A266" s="2" t="s">
         <v>284</v>
       </c>
@@ -9470,7 +10092,7 @@
       <c r="X266" s="3"/>
       <c r="Y266" s="3"/>
     </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="267" x14ac:dyDescent="0.15">
       <c r="A267" s="2" t="s">
         <v>285</v>
       </c>
@@ -9499,7 +10121,7 @@
       <c r="X267" s="3"/>
       <c r="Y267" s="3"/>
     </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="268" x14ac:dyDescent="0.15">
       <c r="A268" s="2" t="s">
         <v>286</v>
       </c>
@@ -9528,7 +10150,7 @@
       <c r="X268" s="3"/>
       <c r="Y268" s="3"/>
     </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="269" x14ac:dyDescent="0.15">
       <c r="A269" s="2" t="s">
         <v>287</v>
       </c>
@@ -9557,7 +10179,7 @@
       <c r="X269" s="3"/>
       <c r="Y269" s="3"/>
     </row>
-    <row r="270" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="270" x14ac:dyDescent="0.15">
       <c r="A270" s="2" t="s">
         <v>288</v>
       </c>
@@ -9586,7 +10208,7 @@
       <c r="X270" s="3"/>
       <c r="Y270" s="3"/>
     </row>
-    <row r="271" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="271" x14ac:dyDescent="0.15">
       <c r="A271" s="2" t="s">
         <v>289</v>
       </c>
@@ -9615,36 +10237,78 @@
       <c r="X271" s="3"/>
       <c r="Y271" s="3"/>
     </row>
-    <row r="272" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="272" x14ac:dyDescent="0.15">
       <c r="A272" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B272" s="3"/>
-      <c r="C272" s="3"/>
-      <c r="D272" s="3"/>
+      <c r="B272" s="3">
+        <v>26.164828033744325</v>
+      </c>
+      <c r="C272" s="3">
+        <v>26.474064346684173</v>
+      </c>
+      <c r="D272" s="3">
+        <v>25.137157107231925</v>
+      </c>
       <c r="E272" s="3"/>
-      <c r="F272" s="3"/>
+      <c r="F272" s="3">
+        <v>27.224848075624582</v>
+      </c>
       <c r="G272" s="3"/>
-      <c r="H272" s="3"/>
-      <c r="I272" s="3"/>
-      <c r="J272" s="3"/>
-      <c r="K272" s="3"/>
-      <c r="L272" s="3"/>
-      <c r="M272" s="3"/>
-      <c r="N272" s="3"/>
+      <c r="H272" s="3">
+        <v>25.567533291058972</v>
+      </c>
+      <c r="I272" s="3">
+        <v>25.862732520846702</v>
+      </c>
+      <c r="J272" s="3">
+        <v>29.822485207100591</v>
+      </c>
+      <c r="K272" s="3">
+        <v>25.648854961832061</v>
+      </c>
+      <c r="L272" s="3">
+        <v>25.714285714285715</v>
+      </c>
+      <c r="M272" s="3">
+        <v>26.387434554973822</v>
+      </c>
+      <c r="N272" s="3">
+        <v>25.912596401028282</v>
+      </c>
       <c r="O272" s="3"/>
-      <c r="P272" s="3"/>
-      <c r="Q272" s="3"/>
-      <c r="R272" s="3"/>
-      <c r="S272" s="3"/>
-      <c r="T272" s="3"/>
-      <c r="U272" s="3"/>
-      <c r="V272" s="3"/>
-      <c r="W272" s="3"/>
-      <c r="X272" s="3"/>
-      <c r="Y272" s="3"/>
-    </row>
-    <row r="273" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="P272" s="3">
+        <v>28.67709815078236</v>
+      </c>
+      <c r="Q272" s="3">
+        <v>25.215759849906192</v>
+      </c>
+      <c r="R272" s="3">
+        <v>26.250000000000004</v>
+      </c>
+      <c r="S272" s="3">
+        <v>26.790697674418606</v>
+      </c>
+      <c r="T272" s="3">
+        <v>26.969899665551839</v>
+      </c>
+      <c r="U272" s="3">
+        <v>28.717948717948723</v>
+      </c>
+      <c r="V272" s="3">
+        <v>24.981412639405207</v>
+      </c>
+      <c r="W272" s="3">
+        <v>25.470625394819962</v>
+      </c>
+      <c r="X272" s="3">
+        <v>27.224848075624582</v>
+      </c>
+      <c r="Y272" s="3">
+        <v>24.996900185988842</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="273" x14ac:dyDescent="0.15">
       <c r="A273" s="2" t="s">
         <v>291</v>
       </c>
@@ -9673,20 +10337,32 @@
       <c r="X273" s="3"/>
       <c r="Y273" s="3"/>
     </row>
-    <row r="274" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="274" x14ac:dyDescent="0.15">
       <c r="A274" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B274" s="3"/>
-      <c r="C274" s="3"/>
-      <c r="D274" s="3"/>
+      <c r="B274" s="3">
+        <v>629.79019452771672</v>
+      </c>
+      <c r="C274" s="3">
+        <v>0.010906919893569076</v>
+      </c>
+      <c r="D274" s="3">
+        <v>630</v>
+      </c>
       <c r="E274" s="3"/>
-      <c r="F274" s="3"/>
+      <c r="F274" s="3">
+        <v>627.91249499590151</v>
+      </c>
       <c r="G274" s="3"/>
-      <c r="H274" s="3"/>
+      <c r="H274" s="3">
+        <v>627.65264946602042</v>
+      </c>
       <c r="I274" s="3"/>
       <c r="J274" s="3"/>
-      <c r="K274" s="3"/>
+      <c r="K274" s="3">
+        <v>627.23141716399357</v>
+      </c>
       <c r="L274" s="3"/>
       <c r="M274" s="3"/>
       <c r="N274" s="3"/>
@@ -9694,15 +10370,19 @@
       <c r="P274" s="3"/>
       <c r="Q274" s="3"/>
       <c r="R274" s="3"/>
-      <c r="S274" s="3"/>
+      <c r="S274" s="3">
+        <v>628.38277313304422</v>
+      </c>
       <c r="T274" s="3"/>
       <c r="U274" s="3"/>
       <c r="V274" s="3"/>
-      <c r="W274" s="3"/>
+      <c r="W274" s="3">
+        <v>432.09284357209418</v>
+      </c>
       <c r="X274" s="3"/>
       <c r="Y274" s="3"/>
     </row>
-    <row r="275" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="275" x14ac:dyDescent="0.15">
       <c r="A275" s="2" t="s">
         <v>293</v>
       </c>
@@ -9731,7 +10411,7 @@
       <c r="X275" s="3"/>
       <c r="Y275" s="3"/>
     </row>
-    <row r="276" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="276" x14ac:dyDescent="0.15">
       <c r="A276" s="2" t="s">
         <v>294</v>
       </c>
@@ -9760,7 +10440,7 @@
       <c r="X276" s="3"/>
       <c r="Y276" s="3"/>
     </row>
-    <row r="277" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="277" x14ac:dyDescent="0.15">
       <c r="A277" s="2" t="s">
         <v>295</v>
       </c>
@@ -9789,7 +10469,7 @@
       <c r="X277" s="3"/>
       <c r="Y277" s="3"/>
     </row>
-    <row r="278" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="278" x14ac:dyDescent="0.15">
       <c r="A278" s="2" t="s">
         <v>296</v>
       </c>
@@ -9818,36 +10498,82 @@
       <c r="X278" s="3"/>
       <c r="Y278" s="3"/>
     </row>
-    <row r="279" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="279" x14ac:dyDescent="0.15">
       <c r="A279" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B279" s="3"/>
-      <c r="C279" s="3"/>
-      <c r="D279" s="3"/>
+      <c r="B279" s="3">
+        <v>171.46034470822048</v>
+      </c>
+      <c r="C279" s="3">
+        <v>158.29162264014534</v>
+      </c>
+      <c r="D279" s="3">
+        <v>185.61538501538342</v>
+      </c>
       <c r="E279" s="3"/>
-      <c r="F279" s="3"/>
-      <c r="G279" s="3"/>
-      <c r="H279" s="3"/>
-      <c r="I279" s="3"/>
-      <c r="J279" s="3"/>
-      <c r="K279" s="3"/>
-      <c r="L279" s="3"/>
-      <c r="M279" s="3"/>
-      <c r="N279" s="3"/>
-      <c r="O279" s="3"/>
-      <c r="P279" s="3"/>
-      <c r="Q279" s="3"/>
-      <c r="R279" s="3"/>
-      <c r="S279" s="3"/>
-      <c r="T279" s="3"/>
-      <c r="U279" s="3"/>
-      <c r="V279" s="3"/>
-      <c r="W279" s="3"/>
-      <c r="X279" s="3"/>
-      <c r="Y279" s="3"/>
-    </row>
-    <row r="280" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="F279" s="3">
+        <v>167.96693512594516</v>
+      </c>
+      <c r="G279" s="3">
+        <v>184.92146078480803</v>
+      </c>
+      <c r="H279" s="3">
+        <v>152.66666666666666</v>
+      </c>
+      <c r="I279" s="3">
+        <v>174.6384898699591</v>
+      </c>
+      <c r="J279" s="3">
+        <v>178.25730089536756</v>
+      </c>
+      <c r="K279" s="3">
+        <v>179.95750040637654</v>
+      </c>
+      <c r="L279" s="3">
+        <v>179.95750040637654</v>
+      </c>
+      <c r="M279" s="3">
+        <v>179.6074437998337</v>
+      </c>
+      <c r="N279" s="3">
+        <v>190.31861448334476</v>
+      </c>
+      <c r="O279" s="3">
+        <v>153.78797786027616</v>
+      </c>
+      <c r="P279" s="3">
+        <v>175.9032323640495</v>
+      </c>
+      <c r="Q279" s="3">
+        <v>178.40005164660454</v>
+      </c>
+      <c r="R279" s="3">
+        <v>178.96496752044641</v>
+      </c>
+      <c r="S279" s="3">
+        <v>190.11965151338327</v>
+      </c>
+      <c r="T279" s="3">
+        <v>201.67229225514635</v>
+      </c>
+      <c r="U279" s="3">
+        <v>177.9505266654416</v>
+      </c>
+      <c r="V279" s="3">
+        <v>177.34008190808652</v>
+      </c>
+      <c r="W279" s="3">
+        <v>178.36762593833231</v>
+      </c>
+      <c r="X279" s="3">
+        <v>171.97996466031563</v>
+      </c>
+      <c r="Y279" s="3">
+        <v>169.76650356111128</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="280" x14ac:dyDescent="0.15">
       <c r="A280" s="2" t="s">
         <v>298</v>
       </c>
@@ -9876,36 +10602,82 @@
       <c r="X280" s="3"/>
       <c r="Y280" s="3"/>
     </row>
-    <row r="281" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="281" x14ac:dyDescent="0.15">
       <c r="A281" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B281" s="3"/>
-      <c r="C281" s="3"/>
-      <c r="D281" s="3"/>
-      <c r="E281" s="3"/>
-      <c r="F281" s="3"/>
-      <c r="G281" s="3"/>
-      <c r="H281" s="3"/>
-      <c r="I281" s="3"/>
-      <c r="J281" s="3"/>
-      <c r="K281" s="3"/>
-      <c r="L281" s="3"/>
-      <c r="M281" s="3"/>
-      <c r="N281" s="3"/>
+      <c r="B281" s="3">
+        <v>810.40356095397419</v>
+      </c>
+      <c r="C281" s="3">
+        <v>809.14399655132752</v>
+      </c>
+      <c r="D281" s="3">
+        <v>814.7729395917097</v>
+      </c>
+      <c r="E281" s="3">
+        <v>808.64614264677073</v>
+      </c>
+      <c r="F281" s="3">
+        <v>814.71731351427616</v>
+      </c>
+      <c r="G281" s="3">
+        <v>811.85704540609231</v>
+      </c>
+      <c r="H281" s="3">
+        <v>817.23792557548143</v>
+      </c>
+      <c r="I281" s="3">
+        <v>807.68185917420885</v>
+      </c>
+      <c r="J281" s="3">
+        <v>604.73255250746263</v>
+      </c>
+      <c r="K281" s="3">
+        <v>808.85106631488156</v>
+      </c>
+      <c r="L281" s="3">
+        <v>813.36095969140274</v>
+      </c>
+      <c r="M281" s="3">
+        <v>820</v>
+      </c>
+      <c r="N281" s="3">
+        <v>810.60612307899714</v>
+      </c>
       <c r="O281" s="3"/>
-      <c r="P281" s="3"/>
-      <c r="Q281" s="3"/>
-      <c r="R281" s="3"/>
-      <c r="S281" s="3"/>
-      <c r="T281" s="3"/>
-      <c r="U281" s="3"/>
-      <c r="V281" s="3"/>
-      <c r="W281" s="3"/>
-      <c r="X281" s="3"/>
-      <c r="Y281" s="3"/>
-    </row>
-    <row r="282" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="P281" s="3">
+        <v>808.83666046648489</v>
+      </c>
+      <c r="Q281" s="3">
+        <v>807.96759912961386</v>
+      </c>
+      <c r="R281" s="3">
+        <v>809.53270662260388</v>
+      </c>
+      <c r="S281" s="3">
+        <v>809.84243563106054</v>
+      </c>
+      <c r="T281" s="3">
+        <v>810.25264267932982</v>
+      </c>
+      <c r="U281" s="3">
+        <v>807.72574072449595</v>
+      </c>
+      <c r="V281" s="3">
+        <v>809.42230419565362</v>
+      </c>
+      <c r="W281" s="3">
+        <v>808.57959637947067</v>
+      </c>
+      <c r="X281" s="3">
+        <v>809.14332663603511</v>
+      </c>
+      <c r="Y281" s="3">
+        <v>811.84685670466479</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="282" x14ac:dyDescent="0.15">
       <c r="A282" s="2" t="s">
         <v>300</v>
       </c>
@@ -9934,7 +10706,7 @@
       <c r="X282" s="3"/>
       <c r="Y282" s="3"/>
     </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="283" x14ac:dyDescent="0.15">
       <c r="A283" s="2" t="s">
         <v>301</v>
       </c>
@@ -9963,7 +10735,7 @@
       <c r="X283" s="3"/>
       <c r="Y283" s="3"/>
     </row>
-    <row r="284" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="284" x14ac:dyDescent="0.15">
       <c r="A284" s="2" t="s">
         <v>302</v>
       </c>
@@ -9992,7 +10764,7 @@
       <c r="X284" s="3"/>
       <c r="Y284" s="3"/>
     </row>
-    <row r="285" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="285" x14ac:dyDescent="0.15">
       <c r="A285" s="2" t="s">
         <v>303</v>
       </c>
@@ -10021,7 +10793,7 @@
       <c r="X285" s="3"/>
       <c r="Y285" s="3"/>
     </row>
-    <row r="286" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="286" x14ac:dyDescent="0.15">
       <c r="A286" s="2" t="s">
         <v>304</v>
       </c>
@@ -10050,7 +10822,7 @@
       <c r="X286" s="3"/>
       <c r="Y286" s="3"/>
     </row>
-    <row r="287" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="287" x14ac:dyDescent="0.15">
       <c r="A287" s="2" t="s">
         <v>305</v>
       </c>
@@ -10079,36 +10851,80 @@
       <c r="X287" s="3"/>
       <c r="Y287" s="3"/>
     </row>
-    <row r="288" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="288" x14ac:dyDescent="0.15">
       <c r="A288" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B288" s="3"/>
-      <c r="C288" s="3"/>
-      <c r="D288" s="3"/>
-      <c r="E288" s="3"/>
-      <c r="F288" s="3"/>
-      <c r="G288" s="3"/>
-      <c r="H288" s="3"/>
-      <c r="I288" s="3"/>
-      <c r="J288" s="3"/>
-      <c r="K288" s="3"/>
-      <c r="L288" s="3"/>
-      <c r="M288" s="3"/>
+      <c r="B288" s="3">
+        <v>1179.1872076855011</v>
+      </c>
+      <c r="C288" s="3">
+        <v>1189.7959034017465</v>
+      </c>
+      <c r="D288" s="3">
+        <v>1185.0208072349719</v>
+      </c>
+      <c r="E288" s="3">
+        <v>1199.1783705878422</v>
+      </c>
+      <c r="F288" s="3">
+        <v>1185.8992388220027</v>
+      </c>
+      <c r="G288" s="3">
+        <v>1194.4141045296403</v>
+      </c>
+      <c r="H288" s="3">
+        <v>1196.2982003595455</v>
+      </c>
+      <c r="I288" s="3">
+        <v>1204.0518807743608</v>
+      </c>
+      <c r="J288" s="3">
+        <v>1201.4471854070086</v>
+      </c>
+      <c r="K288" s="3">
+        <v>1207.8742655142655</v>
+      </c>
+      <c r="L288" s="3">
+        <v>1202.8200843239124</v>
+      </c>
+      <c r="M288" s="3">
+        <v>1203.5135402064275</v>
+      </c>
       <c r="N288" s="3"/>
       <c r="O288" s="3"/>
-      <c r="P288" s="3"/>
-      <c r="Q288" s="3"/>
-      <c r="R288" s="3"/>
-      <c r="S288" s="3"/>
-      <c r="T288" s="3"/>
-      <c r="U288" s="3"/>
-      <c r="V288" s="3"/>
-      <c r="W288" s="3"/>
-      <c r="X288" s="3"/>
-      <c r="Y288" s="3"/>
-    </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="P288" s="3">
+        <v>1202.6057193290753</v>
+      </c>
+      <c r="Q288" s="3">
+        <v>1205.3040429168409</v>
+      </c>
+      <c r="R288" s="3">
+        <v>1203.2352835341339</v>
+      </c>
+      <c r="S288" s="3">
+        <v>1210</v>
+      </c>
+      <c r="T288" s="3">
+        <v>1207.0154548815608</v>
+      </c>
+      <c r="U288" s="3">
+        <v>1206.3213840285555</v>
+      </c>
+      <c r="V288" s="3">
+        <v>1204.4841328329169</v>
+      </c>
+      <c r="W288" s="3">
+        <v>1206.1812300252209</v>
+      </c>
+      <c r="X288" s="3">
+        <v>964.26752899300345</v>
+      </c>
+      <c r="Y288" s="3">
+        <v>1202.8493818985203</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="289" x14ac:dyDescent="0.15">
       <c r="A289" s="2" t="s">
         <v>307</v>
       </c>
@@ -10137,36 +10953,54 @@
       <c r="X289" s="3"/>
       <c r="Y289" s="3"/>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="290" x14ac:dyDescent="0.15">
       <c r="A290" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B290" s="3"/>
+      <c r="B290" s="3">
+        <v>324.75156556758583</v>
+      </c>
       <c r="C290" s="3"/>
-      <c r="D290" s="3"/>
+      <c r="D290" s="3">
+        <v>322.38653411644941</v>
+      </c>
       <c r="E290" s="3"/>
-      <c r="F290" s="3"/>
+      <c r="F290" s="3">
+        <v>319.67133670511436</v>
+      </c>
       <c r="G290" s="3"/>
-      <c r="H290" s="3"/>
+      <c r="H290" s="3">
+        <v>327.64018106357497</v>
+      </c>
       <c r="I290" s="3"/>
       <c r="J290" s="3"/>
-      <c r="K290" s="3"/>
+      <c r="K290" s="3">
+        <v>320.01681526092369</v>
+      </c>
       <c r="L290" s="3"/>
       <c r="M290" s="3"/>
       <c r="N290" s="3"/>
       <c r="O290" s="3"/>
-      <c r="P290" s="3"/>
+      <c r="P290" s="3">
+        <v>171.35722234349939</v>
+      </c>
       <c r="Q290" s="3"/>
-      <c r="R290" s="3"/>
-      <c r="S290" s="3"/>
+      <c r="R290" s="3">
+        <v>190.16772461212756</v>
+      </c>
+      <c r="S290" s="3">
+        <v>323.90163214178733</v>
+      </c>
       <c r="T290" s="3"/>
       <c r="U290" s="3"/>
       <c r="V290" s="3"/>
       <c r="W290" s="3"/>
       <c r="X290" s="3"/>
-      <c r="Y290" s="3"/>
-    </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Y290" s="3">
+        <v>323.6574572766956</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="291" x14ac:dyDescent="0.15">
       <c r="A291" s="2" t="s">
         <v>309</v>
       </c>
@@ -10195,7 +11029,7 @@
       <c r="X291" s="3"/>
       <c r="Y291" s="3"/>
     </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="292" x14ac:dyDescent="0.15">
       <c r="A292" s="2" t="s">
         <v>310</v>
       </c>
@@ -10224,7 +11058,7 @@
       <c r="X292" s="3"/>
       <c r="Y292" s="3"/>
     </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="293" x14ac:dyDescent="0.15">
       <c r="A293" s="2" t="s">
         <v>311</v>
       </c>
@@ -10253,7 +11087,7 @@
       <c r="X293" s="3"/>
       <c r="Y293" s="3"/>
     </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="294" x14ac:dyDescent="0.15">
       <c r="A294" s="2" t="s">
         <v>312</v>
       </c>
@@ -10282,7 +11116,7 @@
       <c r="X294" s="3"/>
       <c r="Y294" s="3"/>
     </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="295" x14ac:dyDescent="0.15">
       <c r="A295" s="2" t="s">
         <v>313</v>
       </c>
@@ -10311,7 +11145,7 @@
       <c r="X295" s="3"/>
       <c r="Y295" s="3"/>
     </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="296" x14ac:dyDescent="0.15">
       <c r="A296" s="2" t="s">
         <v>314</v>
       </c>
@@ -10340,65 +11174,159 @@
       <c r="X296" s="3"/>
       <c r="Y296" s="3"/>
     </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="297" x14ac:dyDescent="0.15">
       <c r="A297" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B297" s="3"/>
-      <c r="C297" s="3"/>
-      <c r="D297" s="3"/>
-      <c r="E297" s="3"/>
-      <c r="F297" s="3"/>
-      <c r="G297" s="3"/>
-      <c r="H297" s="3"/>
-      <c r="I297" s="3"/>
-      <c r="J297" s="3"/>
-      <c r="K297" s="3"/>
-      <c r="L297" s="3"/>
-      <c r="M297" s="3"/>
-      <c r="N297" s="3"/>
-      <c r="O297" s="3"/>
-      <c r="P297" s="3"/>
-      <c r="Q297" s="3"/>
-      <c r="R297" s="3"/>
-      <c r="S297" s="3"/>
-      <c r="T297" s="3"/>
+      <c r="B297" s="3">
+        <v>34.608503742093774</v>
+      </c>
+      <c r="C297" s="3">
+        <v>31.101726801274182</v>
+      </c>
+      <c r="D297" s="3">
+        <v>34.17081479754399</v>
+      </c>
+      <c r="E297" s="3">
+        <v>31.101726801274182</v>
+      </c>
+      <c r="F297" s="3">
+        <v>34.819258966301867</v>
+      </c>
+      <c r="G297" s="3">
+        <v>32.935122161619255</v>
+      </c>
+      <c r="H297" s="3">
+        <v>56.955916863853588</v>
+      </c>
+      <c r="I297" s="3">
+        <v>30.32973121326205</v>
+      </c>
+      <c r="J297" s="3">
+        <v>31.250568474653544</v>
+      </c>
+      <c r="K297" s="3">
+        <v>26.087621036297165</v>
+      </c>
+      <c r="L297" s="3">
+        <v>37.425554497585779</v>
+      </c>
+      <c r="M297" s="3">
+        <v>28.837098998553895</v>
+      </c>
+      <c r="N297" s="3">
+        <v>37.028682049000743</v>
+      </c>
+      <c r="O297" s="3">
+        <v>27.978594826929619</v>
+      </c>
+      <c r="P297" s="3">
+        <v>30.018506635175168</v>
+      </c>
+      <c r="Q297" s="3">
+        <v>33.124339673010681</v>
+      </c>
+      <c r="R297" s="3">
+        <v>30.144095083651365</v>
+      </c>
+      <c r="S297" s="3">
+        <v>30.848186803288918</v>
+      </c>
+      <c r="T297" s="3">
+        <v>29.577622903354676</v>
+      </c>
       <c r="U297" s="3"/>
-      <c r="V297" s="3"/>
-      <c r="W297" s="3"/>
-      <c r="X297" s="3"/>
-      <c r="Y297" s="3"/>
-    </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="V297" s="3">
+        <v>42.012035053181691</v>
+      </c>
+      <c r="W297" s="3">
+        <v>29.739041305796697</v>
+      </c>
+      <c r="X297" s="3">
+        <v>30.630587460563866</v>
+      </c>
+      <c r="Y297" s="3">
+        <v>31.363339640990812</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="298" x14ac:dyDescent="0.15">
       <c r="A298" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B298" s="3"/>
-      <c r="C298" s="3"/>
-      <c r="D298" s="3"/>
-      <c r="E298" s="3"/>
-      <c r="F298" s="3"/>
-      <c r="G298" s="3"/>
-      <c r="H298" s="3"/>
-      <c r="I298" s="3"/>
-      <c r="J298" s="3"/>
-      <c r="K298" s="3"/>
-      <c r="L298" s="3"/>
-      <c r="M298" s="3"/>
-      <c r="N298" s="3"/>
-      <c r="O298" s="3"/>
-      <c r="P298" s="3"/>
-      <c r="Q298" s="3"/>
-      <c r="R298" s="3"/>
-      <c r="S298" s="3"/>
-      <c r="T298" s="3"/>
-      <c r="U298" s="3"/>
-      <c r="V298" s="3"/>
-      <c r="W298" s="3"/>
-      <c r="X298" s="3"/>
-      <c r="Y298" s="3"/>
-    </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B298" s="3">
+        <v>210.76445394538203</v>
+      </c>
+      <c r="C298" s="3">
+        <v>220</v>
+      </c>
+      <c r="D298" s="3">
+        <v>211.76705639545185</v>
+      </c>
+      <c r="E298" s="3">
+        <v>219.83194536987344</v>
+      </c>
+      <c r="F298" s="3">
+        <v>220</v>
+      </c>
+      <c r="G298" s="3">
+        <v>220</v>
+      </c>
+      <c r="H298" s="3">
+        <v>220</v>
+      </c>
+      <c r="I298" s="3">
+        <v>220</v>
+      </c>
+      <c r="J298" s="3">
+        <v>208.96559792064815</v>
+      </c>
+      <c r="K298" s="3">
+        <v>220</v>
+      </c>
+      <c r="L298" s="3">
+        <v>220</v>
+      </c>
+      <c r="M298" s="3">
+        <v>192.30908805004336</v>
+      </c>
+      <c r="N298" s="3">
+        <v>220</v>
+      </c>
+      <c r="O298" s="3">
+        <v>220</v>
+      </c>
+      <c r="P298" s="3">
+        <v>220</v>
+      </c>
+      <c r="Q298" s="3">
+        <v>220</v>
+      </c>
+      <c r="R298" s="3">
+        <v>203.44851872098039</v>
+      </c>
+      <c r="S298" s="3">
+        <v>201.64331293499873</v>
+      </c>
+      <c r="T298" s="3">
+        <v>220</v>
+      </c>
+      <c r="U298" s="3">
+        <v>209.18304515998122</v>
+      </c>
+      <c r="V298" s="3">
+        <v>220</v>
+      </c>
+      <c r="W298" s="3">
+        <v>220</v>
+      </c>
+      <c r="X298" s="3">
+        <v>206.11862690132924</v>
+      </c>
+      <c r="Y298" s="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="299" x14ac:dyDescent="0.15">
       <c r="A299" s="2" t="s">
         <v>317</v>
       </c>
@@ -10427,28 +11355,42 @@
       <c r="X299" s="3"/>
       <c r="Y299" s="3"/>
     </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="300" x14ac:dyDescent="0.15">
       <c r="A300" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B300" s="3"/>
-      <c r="C300" s="3"/>
-      <c r="D300" s="3"/>
+      <c r="B300" s="3">
+        <v>90</v>
+      </c>
+      <c r="C300" s="3">
+        <v>88.931585455564928</v>
+      </c>
+      <c r="D300" s="3">
+        <v>90</v>
+      </c>
       <c r="E300" s="3"/>
       <c r="F300" s="3"/>
       <c r="G300" s="3"/>
-      <c r="H300" s="3"/>
+      <c r="H300" s="3">
+        <v>90</v>
+      </c>
       <c r="I300" s="3"/>
       <c r="J300" s="3"/>
-      <c r="K300" s="3"/>
+      <c r="K300" s="3">
+        <v>87.12879947160053</v>
+      </c>
       <c r="L300" s="3"/>
       <c r="M300" s="3"/>
       <c r="N300" s="3"/>
       <c r="O300" s="3"/>
-      <c r="P300" s="3"/>
+      <c r="P300" s="3">
+        <v>90</v>
+      </c>
       <c r="Q300" s="3"/>
       <c r="R300" s="3"/>
-      <c r="S300" s="3"/>
+      <c r="S300" s="3">
+        <v>90</v>
+      </c>
       <c r="T300" s="3"/>
       <c r="U300" s="3"/>
       <c r="V300" s="3"/>
@@ -10456,7 +11398,7 @@
       <c r="X300" s="3"/>
       <c r="Y300" s="3"/>
     </row>
-    <row r="301" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="301" x14ac:dyDescent="0.15">
       <c r="A301" s="2" t="s">
         <v>319</v>
       </c>
@@ -10485,7 +11427,7 @@
       <c r="X301" s="3"/>
       <c r="Y301" s="3"/>
     </row>
-    <row r="302" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="302" x14ac:dyDescent="0.15">
       <c r="A302" s="2" t="s">
         <v>320</v>
       </c>
@@ -10514,7 +11456,7 @@
       <c r="X302" s="3"/>
       <c r="Y302" s="3"/>
     </row>
-    <row r="303" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="303" x14ac:dyDescent="0.15">
       <c r="A303" s="2" t="s">
         <v>321</v>
       </c>
@@ -10543,7 +11485,7 @@
       <c r="X303" s="3"/>
       <c r="Y303" s="3"/>
     </row>
-    <row r="304" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="304" x14ac:dyDescent="0.15">
       <c r="A304" s="2" t="s">
         <v>322</v>
       </c>
@@ -10572,7 +11514,7 @@
       <c r="X304" s="3"/>
       <c r="Y304" s="3"/>
     </row>
-    <row r="305" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="305" x14ac:dyDescent="0.15">
       <c r="A305" s="2" t="s">
         <v>323</v>
       </c>
@@ -10601,7 +11543,7 @@
       <c r="X305" s="3"/>
       <c r="Y305" s="3"/>
     </row>
-    <row r="306" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="306" x14ac:dyDescent="0.15">
       <c r="A306" s="2" t="s">
         <v>324</v>
       </c>
@@ -10630,7 +11572,7 @@
       <c r="X306" s="3"/>
       <c r="Y306" s="3"/>
     </row>
-    <row r="307" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="307" x14ac:dyDescent="0.15">
       <c r="A307" s="2" t="s">
         <v>325</v>
       </c>
@@ -10659,7 +11601,7 @@
       <c r="X307" s="3"/>
       <c r="Y307" s="3"/>
     </row>
-    <row r="308" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="308" x14ac:dyDescent="0.15">
       <c r="A308" s="2" t="s">
         <v>326</v>
       </c>
@@ -10688,7 +11630,7 @@
       <c r="X308" s="3"/>
       <c r="Y308" s="3"/>
     </row>
-    <row r="309" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="309" x14ac:dyDescent="0.15">
       <c r="A309" s="2" t="s">
         <v>327</v>
       </c>
@@ -10717,7 +11659,7 @@
       <c r="X309" s="3"/>
       <c r="Y309" s="3"/>
     </row>
-    <row r="310" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="310" x14ac:dyDescent="0.15">
       <c r="A310" s="2" t="s">
         <v>328</v>
       </c>
@@ -10746,7 +11688,7 @@
       <c r="X310" s="3"/>
       <c r="Y310" s="3"/>
     </row>
-    <row r="311" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="311" x14ac:dyDescent="0.15">
       <c r="A311" s="2" t="s">
         <v>329</v>
       </c>
@@ -10775,20 +11717,28 @@
       <c r="X311" s="3"/>
       <c r="Y311" s="3"/>
     </row>
-    <row r="312" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="312" x14ac:dyDescent="0.15">
       <c r="A312" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B312" s="3"/>
+      <c r="B312" s="3">
+        <v>659.45134128917539</v>
+      </c>
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
-      <c r="F312" s="3"/>
+      <c r="F312" s="3">
+        <v>475.33842572160012</v>
+      </c>
       <c r="G312" s="3"/>
-      <c r="H312" s="3"/>
+      <c r="H312" s="3">
+        <v>661</v>
+      </c>
       <c r="I312" s="3"/>
       <c r="J312" s="3"/>
-      <c r="K312" s="3"/>
+      <c r="K312" s="3">
+        <v>660.70330567642566</v>
+      </c>
       <c r="L312" s="3"/>
       <c r="M312" s="3"/>
       <c r="N312" s="3"/>
@@ -10796,44 +11746,92 @@
       <c r="P312" s="3"/>
       <c r="Q312" s="3"/>
       <c r="R312" s="3"/>
-      <c r="S312" s="3"/>
-      <c r="T312" s="3"/>
+      <c r="S312" s="3">
+        <v>661</v>
+      </c>
+      <c r="T312" s="3">
+        <v>660.80942183628758</v>
+      </c>
       <c r="U312" s="3"/>
       <c r="V312" s="3"/>
       <c r="W312" s="3"/>
       <c r="X312" s="3"/>
       <c r="Y312" s="3"/>
     </row>
-    <row r="313" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="313" x14ac:dyDescent="0.15">
       <c r="A313" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B313" s="3"/>
-      <c r="C313" s="3"/>
-      <c r="D313" s="3"/>
+      <c r="B313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="C313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="D313" s="3">
+        <v>359.66394780407268</v>
+      </c>
       <c r="E313" s="3"/>
-      <c r="F313" s="3"/>
-      <c r="G313" s="3"/>
-      <c r="H313" s="3"/>
-      <c r="I313" s="3"/>
-      <c r="J313" s="3"/>
-      <c r="K313" s="3"/>
-      <c r="L313" s="3"/>
-      <c r="M313" s="3"/>
-      <c r="N313" s="3"/>
-      <c r="O313" s="3"/>
-      <c r="P313" s="3"/>
-      <c r="Q313" s="3"/>
-      <c r="R313" s="3"/>
-      <c r="S313" s="3"/>
-      <c r="T313" s="3"/>
+      <c r="F313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="G313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="H313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="I313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="J313" s="3">
+        <v>333.48922873596166</v>
+      </c>
+      <c r="K313" s="3">
+        <v>358.21172030501475</v>
+      </c>
+      <c r="L313" s="3">
+        <v>352.47153497178829</v>
+      </c>
+      <c r="M313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="N313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="O313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="P313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="Q313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="R313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="S313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="T313" s="3">
+        <v>372.00000000000045</v>
+      </c>
       <c r="U313" s="3"/>
-      <c r="V313" s="3"/>
-      <c r="W313" s="3"/>
-      <c r="X313" s="3"/>
-      <c r="Y313" s="3"/>
-    </row>
-    <row r="314" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="V313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="W313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+      <c r="X313" s="3">
+        <v>372.0000000000004</v>
+      </c>
+      <c r="Y313" s="3">
+        <v>372.00000000000045</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="314" x14ac:dyDescent="0.15">
       <c r="A314" s="2" t="s">
         <v>332</v>
       </c>
@@ -10862,7 +11860,7 @@
       <c r="X314" s="3"/>
       <c r="Y314" s="3"/>
     </row>
-    <row r="315" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="315" x14ac:dyDescent="0.15">
       <c r="A315" s="2" t="s">
         <v>333</v>
       </c>
@@ -10891,7 +11889,7 @@
       <c r="X315" s="3"/>
       <c r="Y315" s="3"/>
     </row>
-    <row r="316" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="316" x14ac:dyDescent="0.15">
       <c r="A316" s="2" t="s">
         <v>334</v>
       </c>
@@ -10920,7 +11918,7 @@
       <c r="X316" s="3"/>
       <c r="Y316" s="3"/>
     </row>
-    <row r="317" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="317" x14ac:dyDescent="0.15">
       <c r="A317" s="2" t="s">
         <v>335</v>
       </c>
@@ -10949,7 +11947,7 @@
       <c r="X317" s="3"/>
       <c r="Y317" s="3"/>
     </row>
-    <row r="318" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="318" x14ac:dyDescent="0.15">
       <c r="A318" s="2" t="s">
         <v>336</v>
       </c>
@@ -10978,7 +11976,7 @@
       <c r="X318" s="3"/>
       <c r="Y318" s="3"/>
     </row>
-    <row r="319" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="319" x14ac:dyDescent="0.15">
       <c r="A319" s="2" t="s">
         <v>337</v>
       </c>
@@ -11007,20 +12005,28 @@
       <c r="X319" s="3"/>
       <c r="Y319" s="3"/>
     </row>
-    <row r="320" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="320" x14ac:dyDescent="0.15">
       <c r="A320" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B320" s="3"/>
+      <c r="B320" s="3">
+        <v>10.599999999999994</v>
+      </c>
       <c r="C320" s="3"/>
-      <c r="D320" s="3"/>
+      <c r="D320" s="3">
+        <v>10.599999999999994</v>
+      </c>
       <c r="E320" s="3"/>
       <c r="F320" s="3"/>
       <c r="G320" s="3"/>
-      <c r="H320" s="3"/>
+      <c r="H320" s="3">
+        <v>10.599999999999994</v>
+      </c>
       <c r="I320" s="3"/>
       <c r="J320" s="3"/>
-      <c r="K320" s="3"/>
+      <c r="K320" s="3">
+        <v>10.599999999999994</v>
+      </c>
       <c r="L320" s="3"/>
       <c r="M320" s="3"/>
       <c r="N320" s="3"/>
@@ -11028,15 +12034,19 @@
       <c r="P320" s="3"/>
       <c r="Q320" s="3"/>
       <c r="R320" s="3"/>
-      <c r="S320" s="3"/>
+      <c r="S320" s="3">
+        <v>10.599999999999994</v>
+      </c>
       <c r="T320" s="3"/>
       <c r="U320" s="3"/>
       <c r="V320" s="3"/>
       <c r="W320" s="3"/>
       <c r="X320" s="3"/>
-      <c r="Y320" s="3"/>
-    </row>
-    <row r="321" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Y320" s="3">
+        <v>10.599999999999994</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="321" x14ac:dyDescent="0.15">
       <c r="A321" s="2" t="s">
         <v>339</v>
       </c>
@@ -11065,7 +12075,7 @@
       <c r="X321" s="3"/>
       <c r="Y321" s="3"/>
     </row>
-    <row r="322" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="322" x14ac:dyDescent="0.15">
       <c r="A322" s="2" t="s">
         <v>340</v>
       </c>
@@ -11094,7 +12104,7 @@
       <c r="X322" s="3"/>
       <c r="Y322" s="3"/>
     </row>
-    <row r="323" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="323" x14ac:dyDescent="0.15">
       <c r="A323" s="2" t="s">
         <v>341</v>
       </c>
@@ -11123,36 +12133,80 @@
       <c r="X323" s="3"/>
       <c r="Y323" s="3"/>
     </row>
-    <row r="324" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="324" x14ac:dyDescent="0.15">
       <c r="A324" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B324" s="3"/>
-      <c r="C324" s="3"/>
-      <c r="D324" s="3"/>
-      <c r="E324" s="3"/>
-      <c r="F324" s="3"/>
+      <c r="B324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="C324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="D324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="E324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="F324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
       <c r="G324" s="3"/>
-      <c r="H324" s="3"/>
-      <c r="I324" s="3"/>
-      <c r="J324" s="3"/>
-      <c r="K324" s="3"/>
-      <c r="L324" s="3"/>
-      <c r="M324" s="3"/>
-      <c r="N324" s="3"/>
-      <c r="O324" s="3"/>
-      <c r="P324" s="3"/>
-      <c r="Q324" s="3"/>
-      <c r="R324" s="3"/>
-      <c r="S324" s="3"/>
-      <c r="T324" s="3"/>
+      <c r="H324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="I324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="J324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="K324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="L324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="M324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="N324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="O324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="P324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="Q324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="R324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="S324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="T324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
       <c r="U324" s="3"/>
-      <c r="V324" s="3"/>
-      <c r="W324" s="3"/>
-      <c r="X324" s="3"/>
-      <c r="Y324" s="3"/>
-    </row>
-    <row r="325" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="V324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="W324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="X324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+      <c r="Y324" s="3">
+        <v>2.4000000000000057</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="325" x14ac:dyDescent="0.15">
       <c r="A325" s="2" t="s">
         <v>343</v>
       </c>
@@ -11181,7 +12235,7 @@
       <c r="X325" s="3"/>
       <c r="Y325" s="3"/>
     </row>
-    <row r="326" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="326" x14ac:dyDescent="0.15">
       <c r="A326" s="2" t="s">
         <v>344</v>
       </c>
@@ -11210,7 +12264,7 @@
       <c r="X326" s="3"/>
       <c r="Y326" s="3"/>
     </row>
-    <row r="327" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="327" x14ac:dyDescent="0.15">
       <c r="A327" s="2" t="s">
         <v>345</v>
       </c>
@@ -11239,7 +12293,7 @@
       <c r="X327" s="3"/>
       <c r="Y327" s="3"/>
     </row>
-    <row r="328" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="328" x14ac:dyDescent="0.15">
       <c r="A328" s="2" t="s">
         <v>346</v>
       </c>
@@ -11268,7 +12322,7 @@
       <c r="X328" s="3"/>
       <c r="Y328" s="3"/>
     </row>
-    <row r="329" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="329" x14ac:dyDescent="0.15">
       <c r="A329" s="2" t="s">
         <v>347</v>
       </c>
@@ -11297,7 +12351,7 @@
       <c r="X329" s="3"/>
       <c r="Y329" s="3"/>
     </row>
-    <row r="330" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="330" x14ac:dyDescent="0.15">
       <c r="A330" s="2" t="s">
         <v>348</v>
       </c>
@@ -11326,7 +12380,7 @@
       <c r="X330" s="3"/>
       <c r="Y330" s="3"/>
     </row>
-    <row r="331" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="331" x14ac:dyDescent="0.15">
       <c r="A331" s="2" t="s">
         <v>349</v>
       </c>
@@ -11355,7 +12409,7 @@
       <c r="X331" s="3"/>
       <c r="Y331" s="3"/>
     </row>
-    <row r="332" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="332" x14ac:dyDescent="0.15">
       <c r="A332" s="2" t="s">
         <v>350</v>
       </c>
@@ -11384,7 +12438,7 @@
       <c r="X332" s="3"/>
       <c r="Y332" s="3"/>
     </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="333" x14ac:dyDescent="0.15">
       <c r="A333" s="2" t="s">
         <v>351</v>
       </c>
@@ -11413,7 +12467,7 @@
       <c r="X333" s="3"/>
       <c r="Y333" s="3"/>
     </row>
-    <row r="334" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="334" x14ac:dyDescent="0.15">
       <c r="A334" s="2" t="s">
         <v>352</v>
       </c>
@@ -11442,36 +12496,82 @@
       <c r="X334" s="3"/>
       <c r="Y334" s="3"/>
     </row>
-    <row r="335" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="335" x14ac:dyDescent="0.15">
       <c r="A335" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B335" s="3"/>
-      <c r="C335" s="3"/>
-      <c r="D335" s="3"/>
+      <c r="B335" s="3">
+        <v>794.63739981940012</v>
+      </c>
+      <c r="C335" s="3">
+        <v>800</v>
+      </c>
+      <c r="D335" s="3">
+        <v>795.27800370827481</v>
+      </c>
       <c r="E335" s="3"/>
-      <c r="F335" s="3"/>
-      <c r="G335" s="3"/>
-      <c r="H335" s="3"/>
-      <c r="I335" s="3"/>
-      <c r="J335" s="3"/>
-      <c r="K335" s="3"/>
-      <c r="L335" s="3"/>
-      <c r="M335" s="3"/>
-      <c r="N335" s="3"/>
-      <c r="O335" s="3"/>
-      <c r="P335" s="3"/>
-      <c r="Q335" s="3"/>
-      <c r="R335" s="3"/>
-      <c r="S335" s="3"/>
-      <c r="T335" s="3"/>
-      <c r="U335" s="3"/>
-      <c r="V335" s="3"/>
-      <c r="W335" s="3"/>
-      <c r="X335" s="3"/>
-      <c r="Y335" s="3"/>
-    </row>
-    <row r="336" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="F335" s="3">
+        <v>796.78214295624775</v>
+      </c>
+      <c r="G335" s="3">
+        <v>799.11937189215348</v>
+      </c>
+      <c r="H335" s="3">
+        <v>796.68114784732825</v>
+      </c>
+      <c r="I335" s="3">
+        <v>794.98663405654361</v>
+      </c>
+      <c r="J335" s="3">
+        <v>795.30635745128518</v>
+      </c>
+      <c r="K335" s="3">
+        <v>798.71006636009736</v>
+      </c>
+      <c r="L335" s="3">
+        <v>800</v>
+      </c>
+      <c r="M335" s="3">
+        <v>793.67958984815732</v>
+      </c>
+      <c r="N335" s="3">
+        <v>800</v>
+      </c>
+      <c r="O335" s="3">
+        <v>793.3185117026768</v>
+      </c>
+      <c r="P335" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q335" s="3">
+        <v>793.7851041369529</v>
+      </c>
+      <c r="R335" s="3">
+        <v>794.82178711884956</v>
+      </c>
+      <c r="S335" s="3">
+        <v>797.76274696236476</v>
+      </c>
+      <c r="T335" s="3">
+        <v>796.01158169480129</v>
+      </c>
+      <c r="U335" s="3">
+        <v>794.87674609039266</v>
+      </c>
+      <c r="V335" s="3">
+        <v>790.20786047891375</v>
+      </c>
+      <c r="W335" s="3">
+        <v>792.11331585525204</v>
+      </c>
+      <c r="X335" s="3">
+        <v>798.20205275824867</v>
+      </c>
+      <c r="Y335" s="3">
+        <v>792.73097861567976</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="336" x14ac:dyDescent="0.15">
       <c r="A336" s="2" t="s">
         <v>354</v>
       </c>
@@ -11500,7 +12600,7 @@
       <c r="X336" s="3"/>
       <c r="Y336" s="3"/>
     </row>
-    <row r="337" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="337" x14ac:dyDescent="0.15">
       <c r="A337" s="2" t="s">
         <v>355</v>
       </c>
@@ -11529,7 +12629,7 @@
       <c r="X337" s="3"/>
       <c r="Y337" s="3"/>
     </row>
-    <row r="338" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="338" x14ac:dyDescent="0.15">
       <c r="A338" s="2" t="s">
         <v>356</v>
       </c>
@@ -11558,7 +12658,7 @@
       <c r="X338" s="3"/>
       <c r="Y338" s="3"/>
     </row>
-    <row r="339" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="339" x14ac:dyDescent="0.15">
       <c r="A339" s="2" t="s">
         <v>357</v>
       </c>
@@ -11587,7 +12687,7 @@
       <c r="X339" s="3"/>
       <c r="Y339" s="3"/>
     </row>
-    <row r="340" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="340" x14ac:dyDescent="0.15">
       <c r="A340" s="2" t="s">
         <v>358</v>
       </c>
@@ -11616,7 +12716,7 @@
       <c r="X340" s="3"/>
       <c r="Y340" s="3"/>
     </row>
-    <row r="341" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="341" x14ac:dyDescent="0.15">
       <c r="A341" s="2" t="s">
         <v>359</v>
       </c>
@@ -11645,7 +12745,7 @@
       <c r="X341" s="3"/>
       <c r="Y341" s="3"/>
     </row>
-    <row r="342" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="342" x14ac:dyDescent="0.15">
       <c r="A342" s="2" t="s">
         <v>360</v>
       </c>
@@ -11674,7 +12774,7 @@
       <c r="X342" s="3"/>
       <c r="Y342" s="3"/>
     </row>
-    <row r="343" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="343" x14ac:dyDescent="0.15">
       <c r="A343" s="2" t="s">
         <v>361</v>
       </c>
@@ -11703,7 +12803,7 @@
       <c r="X343" s="3"/>
       <c r="Y343" s="3"/>
     </row>
-    <row r="344" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="344" x14ac:dyDescent="0.15">
       <c r="A344" s="2" t="s">
         <v>362</v>
       </c>
@@ -11732,7 +12832,7 @@
       <c r="X344" s="3"/>
       <c r="Y344" s="3"/>
     </row>
-    <row r="345" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="345" x14ac:dyDescent="0.15">
       <c r="A345" s="2" t="s">
         <v>363</v>
       </c>
@@ -11761,7 +12861,7 @@
       <c r="X345" s="3"/>
       <c r="Y345" s="3"/>
     </row>
-    <row r="346" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="346" x14ac:dyDescent="0.15">
       <c r="A346" s="2" t="s">
         <v>364</v>
       </c>
@@ -11790,7 +12890,7 @@
       <c r="X346" s="3"/>
       <c r="Y346" s="3"/>
     </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="347" x14ac:dyDescent="0.15">
       <c r="A347" s="2" t="s">
         <v>365</v>
       </c>
@@ -11819,36 +12919,54 @@
       <c r="X347" s="3"/>
       <c r="Y347" s="3"/>
     </row>
-    <row r="348" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="348" x14ac:dyDescent="0.15">
       <c r="A348" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B348" s="3"/>
-      <c r="C348" s="3"/>
+      <c r="B348" s="3">
+        <v>9.9684302613061497</v>
+      </c>
+      <c r="C348" s="3">
+        <v>9.9684302613061497</v>
+      </c>
       <c r="D348" s="3"/>
       <c r="E348" s="3"/>
-      <c r="F348" s="3"/>
+      <c r="F348" s="3">
+        <v>9.9684302613061497</v>
+      </c>
       <c r="G348" s="3"/>
-      <c r="H348" s="3"/>
-      <c r="I348" s="3"/>
+      <c r="H348" s="3">
+        <v>9.9684302613061497</v>
+      </c>
+      <c r="I348" s="3">
+        <v>9.9684302613061497</v>
+      </c>
       <c r="J348" s="3"/>
-      <c r="K348" s="3"/>
+      <c r="K348" s="3">
+        <v>8.9649589209547447</v>
+      </c>
       <c r="L348" s="3"/>
       <c r="M348" s="3"/>
       <c r="N348" s="3"/>
       <c r="O348" s="3"/>
-      <c r="P348" s="3"/>
+      <c r="P348" s="3">
+        <v>9.9684302613061497</v>
+      </c>
       <c r="Q348" s="3"/>
       <c r="R348" s="3"/>
-      <c r="S348" s="3"/>
+      <c r="S348" s="3">
+        <v>10</v>
+      </c>
       <c r="T348" s="3"/>
       <c r="U348" s="3"/>
       <c r="V348" s="3"/>
       <c r="W348" s="3"/>
       <c r="X348" s="3"/>
-      <c r="Y348" s="3"/>
-    </row>
-    <row r="349" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Y348" s="3">
+        <v>9.9684302613061497</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="349" x14ac:dyDescent="0.15">
       <c r="A349" s="2" t="s">
         <v>367</v>
       </c>
@@ -11877,7 +12995,7 @@
       <c r="X349" s="3"/>
       <c r="Y349" s="3"/>
     </row>
-    <row r="350" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="350" x14ac:dyDescent="0.15">
       <c r="A350" s="2" t="s">
         <v>368</v>
       </c>
@@ -11906,7 +13024,7 @@
       <c r="X350" s="3"/>
       <c r="Y350" s="3"/>
     </row>
-    <row r="351" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="351" x14ac:dyDescent="0.15">
       <c r="A351" s="2" t="s">
         <v>369</v>
       </c>
@@ -11935,7 +13053,7 @@
       <c r="X351" s="3"/>
       <c r="Y351" s="3"/>
     </row>
-    <row r="352" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="352" x14ac:dyDescent="0.15">
       <c r="A352" s="2" t="s">
         <v>370</v>
       </c>
@@ -11964,7 +13082,7 @@
       <c r="X352" s="3"/>
       <c r="Y352" s="3"/>
     </row>
-    <row r="353" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="353" x14ac:dyDescent="0.15">
       <c r="A353" s="2" t="s">
         <v>371</v>
       </c>
@@ -11993,36 +13111,80 @@
       <c r="X353" s="3"/>
       <c r="Y353" s="3"/>
     </row>
-    <row r="354" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="354" x14ac:dyDescent="0.15">
       <c r="A354" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B354" s="3"/>
-      <c r="C354" s="3"/>
-      <c r="D354" s="3"/>
+      <c r="B354" s="3">
+        <v>395.65123272887672</v>
+      </c>
+      <c r="C354" s="3">
+        <v>541.99999999999989</v>
+      </c>
+      <c r="D354" s="3">
+        <v>529.13204384600465</v>
+      </c>
       <c r="E354" s="3"/>
-      <c r="F354" s="3"/>
+      <c r="F354" s="3">
+        <v>417.71695448751785</v>
+      </c>
       <c r="G354" s="3"/>
-      <c r="H354" s="3"/>
-      <c r="I354" s="3"/>
-      <c r="J354" s="3"/>
-      <c r="K354" s="3"/>
-      <c r="L354" s="3"/>
-      <c r="M354" s="3"/>
-      <c r="N354" s="3"/>
-      <c r="O354" s="3"/>
-      <c r="P354" s="3"/>
-      <c r="Q354" s="3"/>
-      <c r="R354" s="3"/>
-      <c r="S354" s="3"/>
-      <c r="T354" s="3"/>
-      <c r="U354" s="3"/>
-      <c r="V354" s="3"/>
-      <c r="W354" s="3"/>
-      <c r="X354" s="3"/>
-      <c r="Y354" s="3"/>
-    </row>
-    <row r="355" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="H354" s="3">
+        <v>345.15306122448982</v>
+      </c>
+      <c r="I354" s="3">
+        <v>406.3395754123174</v>
+      </c>
+      <c r="J354" s="3">
+        <v>523.35657435262999</v>
+      </c>
+      <c r="K354" s="3">
+        <v>388.1807270268967</v>
+      </c>
+      <c r="L354" s="3">
+        <v>430.09738785310214</v>
+      </c>
+      <c r="M354" s="3">
+        <v>477.46019756369537</v>
+      </c>
+      <c r="N354" s="3">
+        <v>432.29362284052917</v>
+      </c>
+      <c r="O354" s="3">
+        <v>398.71761697137805</v>
+      </c>
+      <c r="P354" s="3">
+        <v>372.89010404615624</v>
+      </c>
+      <c r="Q354" s="3">
+        <v>423.66412593122959</v>
+      </c>
+      <c r="R354" s="3">
+        <v>418.15487038008331</v>
+      </c>
+      <c r="S354" s="3">
+        <v>416.89098585413547</v>
+      </c>
+      <c r="T354" s="3">
+        <v>408.50178816008452</v>
+      </c>
+      <c r="U354" s="3">
+        <v>418.11977525925312</v>
+      </c>
+      <c r="V354" s="3">
+        <v>412.89435750920546</v>
+      </c>
+      <c r="W354" s="3">
+        <v>401.54083457643463</v>
+      </c>
+      <c r="X354" s="3">
+        <v>440.75618020746447</v>
+      </c>
+      <c r="Y354" s="3">
+        <v>377.00945900050004</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="355" x14ac:dyDescent="0.15">
       <c r="A355" s="2" t="s">
         <v>373</v>
       </c>
@@ -12051,7 +13213,7 @@
       <c r="X355" s="3"/>
       <c r="Y355" s="3"/>
     </row>
-    <row r="356" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="356" x14ac:dyDescent="0.15">
       <c r="A356" s="2" t="s">
         <v>374</v>
       </c>
@@ -12080,7 +13242,7 @@
       <c r="X356" s="3"/>
       <c r="Y356" s="3"/>
     </row>
-    <row r="357" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="357" x14ac:dyDescent="0.15">
       <c r="A357" s="2" t="s">
         <v>375</v>
       </c>
@@ -12109,36 +13271,80 @@
       <c r="X357" s="3"/>
       <c r="Y357" s="3"/>
     </row>
-    <row r="358" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="358" x14ac:dyDescent="0.15">
       <c r="A358" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B358" s="3"/>
-      <c r="C358" s="3"/>
-      <c r="D358" s="3"/>
-      <c r="E358" s="3"/>
-      <c r="F358" s="3"/>
+      <c r="B358" s="3">
+        <v>561.97885390409044</v>
+      </c>
+      <c r="C358" s="3">
+        <v>554.49505441681674</v>
+      </c>
+      <c r="D358" s="3">
+        <v>570</v>
+      </c>
+      <c r="E358" s="3">
+        <v>554.81335093741779</v>
+      </c>
+      <c r="F358" s="3">
+        <v>570</v>
+      </c>
       <c r="G358" s="3"/>
-      <c r="H358" s="3"/>
-      <c r="I358" s="3"/>
+      <c r="H358" s="3">
+        <v>554.7662783157399</v>
+      </c>
+      <c r="I358" s="3">
+        <v>570</v>
+      </c>
       <c r="J358" s="3"/>
-      <c r="K358" s="3"/>
-      <c r="L358" s="3"/>
-      <c r="M358" s="3"/>
-      <c r="N358" s="3"/>
-      <c r="O358" s="3"/>
-      <c r="P358" s="3"/>
-      <c r="Q358" s="3"/>
-      <c r="R358" s="3"/>
-      <c r="S358" s="3"/>
-      <c r="T358" s="3"/>
-      <c r="U358" s="3"/>
-      <c r="V358" s="3"/>
-      <c r="W358" s="3"/>
-      <c r="X358" s="3"/>
-      <c r="Y358" s="3"/>
-    </row>
-    <row r="359" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="K358" s="3">
+        <v>553.83795989842713</v>
+      </c>
+      <c r="L358" s="3">
+        <v>556.75924071992597</v>
+      </c>
+      <c r="M358" s="3">
+        <v>557.19551854938584</v>
+      </c>
+      <c r="N358" s="3">
+        <v>558.10212228365333</v>
+      </c>
+      <c r="O358" s="3">
+        <v>568.6436010506568</v>
+      </c>
+      <c r="P358" s="3">
+        <v>554.37043590449468</v>
+      </c>
+      <c r="Q358" s="3">
+        <v>556.59302191426468</v>
+      </c>
+      <c r="R358" s="3">
+        <v>562.53071461223704</v>
+      </c>
+      <c r="S358" s="3">
+        <v>555.23672878567766</v>
+      </c>
+      <c r="T358" s="3">
+        <v>554.64408438344356</v>
+      </c>
+      <c r="U358" s="3">
+        <v>554.27550938607567</v>
+      </c>
+      <c r="V358" s="3">
+        <v>565.52336026486921</v>
+      </c>
+      <c r="W358" s="3">
+        <v>562.4404635459789</v>
+      </c>
+      <c r="X358" s="3">
+        <v>559.38397600706628</v>
+      </c>
+      <c r="Y358" s="3">
+        <v>563.9800286093946</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="359" x14ac:dyDescent="0.15">
       <c r="A359" s="2" t="s">
         <v>377</v>
       </c>
@@ -12167,7 +13373,7 @@
       <c r="X359" s="3"/>
       <c r="Y359" s="3"/>
     </row>
-    <row r="360" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="360" x14ac:dyDescent="0.15">
       <c r="A360" s="2" t="s">
         <v>378</v>
       </c>
@@ -12196,7 +13402,7 @@
       <c r="X360" s="3"/>
       <c r="Y360" s="3"/>
     </row>
-    <row r="361" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="361" x14ac:dyDescent="0.15">
       <c r="A361" s="2" t="s">
         <v>379</v>
       </c>
@@ -12225,36 +13431,50 @@
       <c r="X361" s="3"/>
       <c r="Y361" s="3"/>
     </row>
-    <row r="362" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="362" x14ac:dyDescent="0.15">
       <c r="A362" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B362" s="3"/>
-      <c r="C362" s="3"/>
+      <c r="B362" s="3">
+        <v>1015.5214625966495</v>
+      </c>
+      <c r="C362" s="3">
+        <v>1060</v>
+      </c>
       <c r="D362" s="3"/>
       <c r="E362" s="3"/>
-      <c r="F362" s="3"/>
+      <c r="F362" s="3">
+        <v>1003.5915356241505</v>
+      </c>
       <c r="G362" s="3"/>
-      <c r="H362" s="3"/>
+      <c r="H362" s="3">
+        <v>1012.1707061033442</v>
+      </c>
       <c r="I362" s="3"/>
       <c r="J362" s="3"/>
-      <c r="K362" s="3"/>
+      <c r="K362" s="3">
+        <v>1025.4194472422703</v>
+      </c>
       <c r="L362" s="3"/>
       <c r="M362" s="3"/>
       <c r="N362" s="3"/>
       <c r="O362" s="3"/>
       <c r="P362" s="3"/>
-      <c r="Q362" s="3"/>
+      <c r="Q362" s="3">
+        <v>1032.9847170301844</v>
+      </c>
       <c r="R362" s="3"/>
       <c r="S362" s="3"/>
-      <c r="T362" s="3"/>
+      <c r="T362" s="3">
+        <v>576.77110679323698</v>
+      </c>
       <c r="U362" s="3"/>
       <c r="V362" s="3"/>
       <c r="W362" s="3"/>
       <c r="X362" s="3"/>
       <c r="Y362" s="3"/>
     </row>
-    <row r="363" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="363" x14ac:dyDescent="0.15">
       <c r="A363" s="2" t="s">
         <v>381</v>
       </c>
@@ -12283,7 +13503,7 @@
       <c r="X363" s="3"/>
       <c r="Y363" s="3"/>
     </row>
-    <row r="364" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="364" x14ac:dyDescent="0.15">
       <c r="A364" s="2" t="s">
         <v>382</v>
       </c>
@@ -12312,7 +13532,7 @@
       <c r="X364" s="3"/>
       <c r="Y364" s="3"/>
     </row>
-    <row r="365" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="365" x14ac:dyDescent="0.15">
       <c r="A365" s="2" t="s">
         <v>383</v>
       </c>
@@ -12341,7 +13561,7 @@
       <c r="X365" s="3"/>
       <c r="Y365" s="3"/>
     </row>
-    <row r="366" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="366" x14ac:dyDescent="0.15">
       <c r="A366" s="2" t="s">
         <v>384</v>
       </c>
@@ -12370,28 +13590,46 @@
       <c r="X366" s="3"/>
       <c r="Y366" s="3"/>
     </row>
-    <row r="367" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="367" x14ac:dyDescent="0.15">
       <c r="A367" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B367" s="3"/>
+      <c r="B367" s="3">
+        <v>1825.090690554003</v>
+      </c>
       <c r="C367" s="3"/>
-      <c r="D367" s="3"/>
+      <c r="D367" s="3">
+        <v>1365.1493147771075</v>
+      </c>
       <c r="E367" s="3"/>
-      <c r="F367" s="3"/>
+      <c r="F367" s="3">
+        <v>1821.603188911583</v>
+      </c>
       <c r="G367" s="3"/>
-      <c r="H367" s="3"/>
-      <c r="I367" s="3"/>
+      <c r="H367" s="3">
+        <v>1484.6280364212789</v>
+      </c>
+      <c r="I367" s="3">
+        <v>1823.5545311556255</v>
+      </c>
       <c r="J367" s="3"/>
-      <c r="K367" s="3"/>
-      <c r="L367" s="3"/>
+      <c r="K367" s="3">
+        <v>1836.2642188386149</v>
+      </c>
+      <c r="L367" s="3">
+        <v>1095.7772633322313</v>
+      </c>
       <c r="M367" s="3"/>
       <c r="N367" s="3"/>
       <c r="O367" s="3"/>
       <c r="P367" s="3"/>
       <c r="Q367" s="3"/>
-      <c r="R367" s="3"/>
-      <c r="S367" s="3"/>
+      <c r="R367" s="3">
+        <v>1902</v>
+      </c>
+      <c r="S367" s="3">
+        <v>489.7233515687031</v>
+      </c>
       <c r="T367" s="3"/>
       <c r="U367" s="3"/>
       <c r="V367" s="3"/>
@@ -12399,7 +13637,7 @@
       <c r="X367" s="3"/>
       <c r="Y367" s="3"/>
     </row>
-    <row r="368" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="368" x14ac:dyDescent="0.15">
       <c r="A368" s="2" t="s">
         <v>386</v>
       </c>
@@ -12428,7 +13666,7 @@
       <c r="X368" s="3"/>
       <c r="Y368" s="3"/>
     </row>
-    <row r="369" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="369" x14ac:dyDescent="0.15">
       <c r="A369" s="2" t="s">
         <v>387</v>
       </c>
@@ -12457,7 +13695,7 @@
       <c r="X369" s="3"/>
       <c r="Y369" s="3"/>
     </row>
-    <row r="370" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="370" x14ac:dyDescent="0.15">
       <c r="A370" s="2" t="s">
         <v>388</v>
       </c>
@@ -12486,20 +13724,30 @@
       <c r="X370" s="3"/>
       <c r="Y370" s="3"/>
     </row>
-    <row r="371" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="371" x14ac:dyDescent="0.15">
       <c r="A371" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B371" s="3"/>
+      <c r="B371" s="3">
+        <v>294.00657245456074</v>
+      </c>
       <c r="C371" s="3"/>
-      <c r="D371" s="3"/>
+      <c r="D371" s="3">
+        <v>295.93758815150028</v>
+      </c>
       <c r="E371" s="3"/>
-      <c r="F371" s="3"/>
+      <c r="F371" s="3">
+        <v>289.29823544861148</v>
+      </c>
       <c r="G371" s="3"/>
-      <c r="H371" s="3"/>
+      <c r="H371" s="3">
+        <v>295.34982396276524</v>
+      </c>
       <c r="I371" s="3"/>
       <c r="J371" s="3"/>
-      <c r="K371" s="3"/>
+      <c r="K371" s="3">
+        <v>291.27470709639624</v>
+      </c>
       <c r="L371" s="3"/>
       <c r="M371" s="3"/>
       <c r="N371" s="3"/>
@@ -12507,7 +13755,9 @@
       <c r="P371" s="3"/>
       <c r="Q371" s="3"/>
       <c r="R371" s="3"/>
-      <c r="S371" s="3"/>
+      <c r="S371" s="3">
+        <v>290.01349196579139</v>
+      </c>
       <c r="T371" s="3"/>
       <c r="U371" s="3"/>
       <c r="V371" s="3"/>
@@ -12515,7 +13765,7 @@
       <c r="X371" s="3"/>
       <c r="Y371" s="3"/>
     </row>
-    <row r="372" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="372" x14ac:dyDescent="0.15">
       <c r="A372" s="2" t="s">
         <v>390</v>
       </c>
@@ -12544,7 +13794,7 @@
       <c r="X372" s="3"/>
       <c r="Y372" s="3"/>
     </row>
-    <row r="373" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="373" x14ac:dyDescent="0.15">
       <c r="A373" s="2" t="s">
         <v>391</v>
       </c>
@@ -12573,7 +13823,7 @@
       <c r="X373" s="3"/>
       <c r="Y373" s="3"/>
     </row>
-    <row r="374" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="374" x14ac:dyDescent="0.15">
       <c r="A374" s="2" t="s">
         <v>392</v>
       </c>
@@ -12602,7 +13852,7 @@
       <c r="X374" s="3"/>
       <c r="Y374" s="3"/>
     </row>
-    <row r="375" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="375" x14ac:dyDescent="0.15">
       <c r="A375" s="2" t="s">
         <v>393</v>
       </c>
@@ -12631,7 +13881,7 @@
       <c r="X375" s="3"/>
       <c r="Y375" s="3"/>
     </row>
-    <row r="376" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="376" x14ac:dyDescent="0.15">
       <c r="A376" s="2" t="s">
         <v>394</v>
       </c>
@@ -12660,7 +13910,7 @@
       <c r="X376" s="3"/>
       <c r="Y376" s="3"/>
     </row>
-    <row r="377" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="377" x14ac:dyDescent="0.15">
       <c r="A377" s="2" t="s">
         <v>395</v>
       </c>
@@ -12689,7 +13939,7 @@
       <c r="X377" s="3"/>
       <c r="Y377" s="3"/>
     </row>
-    <row r="378" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="378" x14ac:dyDescent="0.15">
       <c r="A378" s="2" t="s">
         <v>396</v>
       </c>
@@ -12718,7 +13968,7 @@
       <c r="X378" s="3"/>
       <c r="Y378" s="3"/>
     </row>
-    <row r="379" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="379" x14ac:dyDescent="0.15">
       <c r="A379" s="2" t="s">
         <v>397</v>
       </c>
@@ -12747,20 +13997,30 @@
       <c r="X379" s="3"/>
       <c r="Y379" s="3"/>
     </row>
-    <row r="380" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="380" x14ac:dyDescent="0.15">
       <c r="A380" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B380" s="3"/>
+      <c r="B380" s="3">
+        <v>30</v>
+      </c>
       <c r="C380" s="3"/>
-      <c r="D380" s="3"/>
+      <c r="D380" s="3">
+        <v>30</v>
+      </c>
       <c r="E380" s="3"/>
-      <c r="F380" s="3"/>
+      <c r="F380" s="3">
+        <v>30</v>
+      </c>
       <c r="G380" s="3"/>
-      <c r="H380" s="3"/>
+      <c r="H380" s="3">
+        <v>30.000000000000004</v>
+      </c>
       <c r="I380" s="3"/>
       <c r="J380" s="3"/>
-      <c r="K380" s="3"/>
+      <c r="K380" s="3">
+        <v>30</v>
+      </c>
       <c r="L380" s="3"/>
       <c r="M380" s="3"/>
       <c r="N380" s="3"/>
@@ -12768,15 +14028,21 @@
       <c r="P380" s="3"/>
       <c r="Q380" s="3"/>
       <c r="R380" s="3"/>
-      <c r="S380" s="3"/>
-      <c r="T380" s="3"/>
+      <c r="S380" s="3">
+        <v>30.000000000000004</v>
+      </c>
+      <c r="T380" s="3">
+        <v>30</v>
+      </c>
       <c r="U380" s="3"/>
       <c r="V380" s="3"/>
       <c r="W380" s="3"/>
       <c r="X380" s="3"/>
-      <c r="Y380" s="3"/>
-    </row>
-    <row r="381" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="Y380" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="381" x14ac:dyDescent="0.15">
       <c r="A381" s="2" t="s">
         <v>399</v>
       </c>
@@ -12805,7 +14071,7 @@
       <c r="X381" s="3"/>
       <c r="Y381" s="3"/>
     </row>
-    <row r="382" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="382" x14ac:dyDescent="0.15">
       <c r="A382" s="2" t="s">
         <v>400</v>
       </c>
@@ -12834,7 +14100,7 @@
       <c r="X382" s="3"/>
       <c r="Y382" s="3"/>
     </row>
-    <row r="383" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="383" x14ac:dyDescent="0.15">
       <c r="A383" s="2" t="s">
         <v>401</v>
       </c>
@@ -12863,7 +14129,7 @@
       <c r="X383" s="3"/>
       <c r="Y383" s="3"/>
     </row>
-    <row r="384" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="384" x14ac:dyDescent="0.15">
       <c r="A384" s="2" t="s">
         <v>402</v>
       </c>
@@ -12892,7 +14158,7 @@
       <c r="X384" s="3"/>
       <c r="Y384" s="3"/>
     </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="385" x14ac:dyDescent="0.15">
       <c r="A385" s="2" t="s">
         <v>403</v>
       </c>
@@ -12921,7 +14187,7 @@
       <c r="X385" s="3"/>
       <c r="Y385" s="3"/>
     </row>
-    <row r="386" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="386" x14ac:dyDescent="0.15">
       <c r="A386" s="2" t="s">
         <v>404</v>
       </c>
@@ -12950,7 +14216,7 @@
       <c r="X386" s="3"/>
       <c r="Y386" s="3"/>
     </row>
-    <row r="387" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="387" x14ac:dyDescent="0.15">
       <c r="A387" s="2" t="s">
         <v>405</v>
       </c>
@@ -12979,7 +14245,7 @@
       <c r="X387" s="3"/>
       <c r="Y387" s="3"/>
     </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="388" x14ac:dyDescent="0.15">
       <c r="A388" s="2" t="s">
         <v>406</v>
       </c>
@@ -13008,7 +14274,7 @@
       <c r="X388" s="3"/>
       <c r="Y388" s="3"/>
     </row>
-    <row r="389" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="389" x14ac:dyDescent="0.15">
       <c r="A389" s="2" t="s">
         <v>407</v>
       </c>
@@ -13037,7 +14303,7 @@
       <c r="X389" s="3"/>
       <c r="Y389" s="3"/>
     </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="390" x14ac:dyDescent="0.15">
       <c r="A390" s="2" t="s">
         <v>408</v>
       </c>
@@ -13066,7 +14332,7 @@
       <c r="X390" s="3"/>
       <c r="Y390" s="3"/>
     </row>
-    <row r="391" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="391" x14ac:dyDescent="0.15">
       <c r="A391" s="2" t="s">
         <v>409</v>
       </c>
@@ -13095,7 +14361,7 @@
       <c r="X391" s="3"/>
       <c r="Y391" s="3"/>
     </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="392" x14ac:dyDescent="0.15">
       <c r="A392" s="2" t="s">
         <v>410</v>
       </c>
@@ -13124,7 +14390,7 @@
       <c r="X392" s="3"/>
       <c r="Y392" s="3"/>
     </row>
-    <row r="393" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="393" x14ac:dyDescent="0.15">
       <c r="A393" s="2" t="s">
         <v>411</v>
       </c>
@@ -13153,7 +14419,7 @@
       <c r="X393" s="3"/>
       <c r="Y393" s="3"/>
     </row>
-    <row r="394" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="394" x14ac:dyDescent="0.15">
       <c r="A394" s="2" t="s">
         <v>412</v>
       </c>
@@ -13182,7 +14448,7 @@
       <c r="X394" s="3"/>
       <c r="Y394" s="3"/>
     </row>
-    <row r="395" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="395" x14ac:dyDescent="0.15">
       <c r="A395" s="2" t="s">
         <v>413</v>
       </c>
@@ -13211,7 +14477,7 @@
       <c r="X395" s="3"/>
       <c r="Y395" s="3"/>
     </row>
-    <row r="396" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="396" x14ac:dyDescent="0.15">
       <c r="A396" s="2" t="s">
         <v>414</v>
       </c>
@@ -13240,7 +14506,7 @@
       <c r="X396" s="3"/>
       <c r="Y396" s="3"/>
     </row>
-    <row r="397" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="397" x14ac:dyDescent="0.15">
       <c r="A397" s="2" t="s">
         <v>415</v>
       </c>
@@ -13269,7 +14535,7 @@
       <c r="X397" s="3"/>
       <c r="Y397" s="3"/>
     </row>
-    <row r="398" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="398" x14ac:dyDescent="0.15">
       <c r="A398" s="2" t="s">
         <v>416</v>
       </c>
@@ -13298,7 +14564,7 @@
       <c r="X398" s="3"/>
       <c r="Y398" s="3"/>
     </row>
-    <row r="399" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="399" x14ac:dyDescent="0.15">
       <c r="A399" s="2" t="s">
         <v>417</v>
       </c>
@@ -13327,7 +14593,7 @@
       <c r="X399" s="3"/>
       <c r="Y399" s="3"/>
     </row>
-    <row r="400" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="400" x14ac:dyDescent="0.15">
       <c r="A400" s="2" t="s">
         <v>418</v>
       </c>
@@ -13356,36 +14622,80 @@
       <c r="X400" s="3"/>
       <c r="Y400" s="3"/>
     </row>
-    <row r="401" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="401" x14ac:dyDescent="0.15">
       <c r="A401" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="B401" s="3"/>
-      <c r="C401" s="3"/>
-      <c r="D401" s="3"/>
-      <c r="E401" s="3"/>
-      <c r="F401" s="3"/>
+      <c r="B401" s="3">
+        <v>3207.8843843138247</v>
+      </c>
+      <c r="C401" s="3">
+        <v>3239.8660531028386</v>
+      </c>
+      <c r="D401" s="3">
+        <v>3239.8660531028386</v>
+      </c>
+      <c r="E401" s="3">
+        <v>2430.6534612370292</v>
+      </c>
+      <c r="F401" s="3">
+        <v>3239.8660531028386</v>
+      </c>
       <c r="G401" s="3"/>
-      <c r="H401" s="3"/>
-      <c r="I401" s="3"/>
+      <c r="H401" s="3">
+        <v>3239.8660531028386</v>
+      </c>
+      <c r="I401" s="3">
+        <v>4295</v>
+      </c>
       <c r="J401" s="3"/>
-      <c r="K401" s="3"/>
-      <c r="L401" s="3"/>
-      <c r="M401" s="3"/>
-      <c r="N401" s="3"/>
-      <c r="O401" s="3"/>
-      <c r="P401" s="3"/>
-      <c r="Q401" s="3"/>
-      <c r="R401" s="3"/>
-      <c r="S401" s="3"/>
-      <c r="T401" s="3"/>
-      <c r="U401" s="3"/>
-      <c r="V401" s="3"/>
-      <c r="W401" s="3"/>
-      <c r="X401" s="3"/>
-      <c r="Y401" s="3"/>
-    </row>
-    <row r="402" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="K401" s="3">
+        <v>3118.303581706843</v>
+      </c>
+      <c r="L401" s="3">
+        <v>3112.1733119060632</v>
+      </c>
+      <c r="M401" s="3">
+        <v>3176.2707986761843</v>
+      </c>
+      <c r="N401" s="3">
+        <v>3300.5087846319825</v>
+      </c>
+      <c r="O401" s="3">
+        <v>4106.2239881949235</v>
+      </c>
+      <c r="P401" s="3">
+        <v>3220.8748539963058</v>
+      </c>
+      <c r="Q401" s="3">
+        <v>3177.8378077433613</v>
+      </c>
+      <c r="R401" s="3">
+        <v>3216.4250255735819</v>
+      </c>
+      <c r="S401" s="3">
+        <v>3118.9841737534648</v>
+      </c>
+      <c r="T401" s="3">
+        <v>3227.584963479791</v>
+      </c>
+      <c r="U401" s="3">
+        <v>4295</v>
+      </c>
+      <c r="V401" s="3">
+        <v>2902.6259188087147</v>
+      </c>
+      <c r="W401" s="3">
+        <v>3227.584963479791</v>
+      </c>
+      <c r="X401" s="3">
+        <v>3115.869788237389</v>
+      </c>
+      <c r="Y401" s="3">
+        <v>3926.6452761914543</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="402" x14ac:dyDescent="0.15">
       <c r="A402" s="2" t="s">
         <v>420</v>
       </c>
@@ -13414,7 +14724,7 @@
       <c r="X402" s="3"/>
       <c r="Y402" s="3"/>
     </row>
-    <row r="403" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="403" x14ac:dyDescent="0.15">
       <c r="A403" s="2" t="s">
         <v>421</v>
       </c>
@@ -13443,7 +14753,7 @@
       <c r="X403" s="3"/>
       <c r="Y403" s="3"/>
     </row>
-    <row r="404" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="404" x14ac:dyDescent="0.15">
       <c r="A404" s="2" t="s">
         <v>422</v>
       </c>
@@ -13472,7 +14782,7 @@
       <c r="X404" s="3"/>
       <c r="Y404" s="3"/>
     </row>
-    <row r="405" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="405" x14ac:dyDescent="0.15">
       <c r="A405" s="2" t="s">
         <v>423</v>
       </c>
@@ -13501,7 +14811,7 @@
       <c r="X405" s="3"/>
       <c r="Y405" s="3"/>
     </row>
-    <row r="406" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="406" x14ac:dyDescent="0.15">
       <c r="A406" s="2" t="s">
         <v>424</v>
       </c>
@@ -13530,7 +14840,7 @@
       <c r="X406" s="3"/>
       <c r="Y406" s="3"/>
     </row>
-    <row r="407" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="407" x14ac:dyDescent="0.15">
       <c r="A407" s="2" t="s">
         <v>425</v>
       </c>
@@ -13559,7 +14869,7 @@
       <c r="X407" s="3"/>
       <c r="Y407" s="3"/>
     </row>
-    <row r="408" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="408" x14ac:dyDescent="0.15">
       <c r="A408" s="2" t="s">
         <v>426</v>
       </c>
@@ -13588,7 +14898,7 @@
       <c r="X408" s="3"/>
       <c r="Y408" s="3"/>
     </row>
-    <row r="409" spans="1:25" x14ac:dyDescent="0.15">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="409" x14ac:dyDescent="0.15">
       <c r="A409" s="16" t="s">
         <v>432</v>
       </c>
